--- a/research/traditional_assets/database/data/singapore/singapore_steel.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_steel.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08830218928668868</v>
+        <v>0.08818942556490132</v>
       </c>
       <c r="C2">
-        <v>30.61208492727135</v>
+        <v>30.32769889773396</v>
       </c>
       <c r="D2">
-        <v>24.27208492727135</v>
+        <v>24.30269889773396</v>
       </c>
       <c r="E2">
-        <v>-19.7</v>
+        <v>-19.385</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="G2">
         <v>6.34</v>
@@ -1445,28 +1445,28 @@
         <v>5.2425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0158445</v>
       </c>
       <c r="N2">
-        <v>5.2425</v>
+        <v>5.2266555</v>
       </c>
       <c r="O2">
-        <v>0.891225</v>
+        <v>0.888531435</v>
       </c>
       <c r="P2">
-        <v>4.351274999999999</v>
+        <v>4.338124065</v>
       </c>
       <c r="Q2">
-        <v>6.421275</v>
+        <v>6.408124064999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08830218928668868</v>
+        <v>0.08865852077262759</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9898041748874731</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>330.87191138881</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08818942556490132</v>
+        <v>0.08807666184311394</v>
       </c>
       <c r="C3">
-        <v>30.32769889773396</v>
+        <v>30.04339019149014</v>
       </c>
       <c r="D3">
-        <v>24.30269889773396</v>
+        <v>24.33339019149014</v>
       </c>
       <c r="E3">
-        <v>-19.385</v>
+        <v>-19.07</v>
       </c>
       <c r="F3">
-        <v>0.315</v>
+        <v>0.63</v>
       </c>
       <c r="G3">
         <v>6.34</v>
@@ -1527,28 +1527,28 @@
         <v>5.2425</v>
       </c>
       <c r="M3">
-        <v>0.0158445</v>
+        <v>0.031689</v>
       </c>
       <c r="N3">
-        <v>5.2266555</v>
+        <v>5.210811</v>
       </c>
       <c r="O3">
-        <v>0.888531435</v>
+        <v>0.88583787</v>
       </c>
       <c r="P3">
-        <v>4.338124065</v>
+        <v>4.32497313</v>
       </c>
       <c r="Q3">
-        <v>6.408124064999999</v>
+        <v>6.39497313</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08865852077262759</v>
+        <v>0.0890221243297081</v>
       </c>
       <c r="T3">
-        <v>0.9898041748874731</v>
+        <v>0.998201485674552</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>330.87191138881</v>
+        <v>165.435955694405</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08807666184311394</v>
+        <v>0.08796389812132656</v>
       </c>
       <c r="C4">
-        <v>30.04339019149014</v>
+        <v>29.75915910185946</v>
       </c>
       <c r="D4">
-        <v>24.33339019149014</v>
+        <v>24.36415910185946</v>
       </c>
       <c r="E4">
-        <v>-19.07</v>
+        <v>-18.755</v>
       </c>
       <c r="F4">
-        <v>0.63</v>
+        <v>0.945</v>
       </c>
       <c r="G4">
         <v>6.34</v>
@@ -1609,28 +1609,28 @@
         <v>5.2425</v>
       </c>
       <c r="M4">
-        <v>0.031689</v>
+        <v>0.04753349999999999</v>
       </c>
       <c r="N4">
-        <v>5.210811</v>
+        <v>5.1949665</v>
       </c>
       <c r="O4">
-        <v>0.88583787</v>
+        <v>0.883144305</v>
       </c>
       <c r="P4">
-        <v>4.32497313</v>
+        <v>4.311822195</v>
       </c>
       <c r="Q4">
-        <v>6.39497313</v>
+        <v>6.381822195</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0890221243297081</v>
+        <v>0.08939322486734697</v>
       </c>
       <c r="T4">
-        <v>0.998201485674552</v>
+        <v>1.00677193689023</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>165.435955694405</v>
+        <v>110.2906371296033</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08796389812132656</v>
+        <v>0.0878511343995392</v>
       </c>
       <c r="C5">
-        <v>29.75915910185946</v>
+        <v>29.47500592364701</v>
       </c>
       <c r="D5">
-        <v>24.36415910185946</v>
+        <v>24.39500592364701</v>
       </c>
       <c r="E5">
-        <v>-18.755</v>
+        <v>-18.44</v>
       </c>
       <c r="F5">
-        <v>0.945</v>
+        <v>1.26</v>
       </c>
       <c r="G5">
         <v>6.34</v>
@@ -1691,28 +1691,28 @@
         <v>5.2425</v>
       </c>
       <c r="M5">
-        <v>0.04753349999999999</v>
+        <v>0.063378</v>
       </c>
       <c r="N5">
-        <v>5.1949665</v>
+        <v>5.179122</v>
       </c>
       <c r="O5">
-        <v>0.883144305</v>
+        <v>0.88045074</v>
       </c>
       <c r="P5">
-        <v>4.311822195</v>
+        <v>4.29867126</v>
       </c>
       <c r="Q5">
-        <v>6.381822195</v>
+        <v>6.368671259999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08939322486734697</v>
+        <v>0.08977205666618668</v>
       </c>
       <c r="T5">
-        <v>1.00677193689023</v>
+        <v>1.015520939172902</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>110.2906371296033</v>
+        <v>82.71797784720249</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0878511343995392</v>
+        <v>0.08773837067775184</v>
       </c>
       <c r="C6">
-        <v>29.47500592364701</v>
+        <v>29.19093095315273</v>
       </c>
       <c r="D6">
-        <v>24.39500592364701</v>
+        <v>24.42593095315273</v>
       </c>
       <c r="E6">
-        <v>-18.44</v>
+        <v>-18.125</v>
       </c>
       <c r="F6">
-        <v>1.26</v>
+        <v>1.575</v>
       </c>
       <c r="G6">
         <v>6.34</v>
@@ -1773,28 +1773,28 @@
         <v>5.2425</v>
       </c>
       <c r="M6">
-        <v>0.063378</v>
+        <v>0.0792225</v>
       </c>
       <c r="N6">
-        <v>5.179122</v>
+        <v>5.1632775</v>
       </c>
       <c r="O6">
-        <v>0.88045074</v>
+        <v>0.8777571749999999</v>
       </c>
       <c r="P6">
-        <v>4.29867126</v>
+        <v>4.285520324999999</v>
       </c>
       <c r="Q6">
-        <v>6.368671259999999</v>
+        <v>6.355520324999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08977205666618668</v>
+        <v>0.09015886387131772</v>
       </c>
       <c r="T6">
-        <v>1.015520939172902</v>
+        <v>1.024454130977314</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.71797784720249</v>
+        <v>66.17438227776199</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08773837067775184</v>
+        <v>0.08762560695596444</v>
       </c>
       <c r="C7">
-        <v>29.19093095315273</v>
+        <v>28.90693448818092</v>
       </c>
       <c r="D7">
-        <v>24.42593095315273</v>
+        <v>24.45693448818092</v>
       </c>
       <c r="E7">
-        <v>-18.125</v>
+        <v>-17.81</v>
       </c>
       <c r="F7">
-        <v>1.575</v>
+        <v>1.89</v>
       </c>
       <c r="G7">
         <v>6.34</v>
@@ -1855,28 +1855,28 @@
         <v>5.2425</v>
       </c>
       <c r="M7">
-        <v>0.0792225</v>
+        <v>0.095067</v>
       </c>
       <c r="N7">
-        <v>5.1632775</v>
+        <v>5.147432999999999</v>
       </c>
       <c r="O7">
-        <v>0.8777571749999999</v>
+        <v>0.87506361</v>
       </c>
       <c r="P7">
-        <v>4.285520324999999</v>
+        <v>4.27236939</v>
       </c>
       <c r="Q7">
-        <v>6.355520324999999</v>
+        <v>6.34236939</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09015886387131772</v>
+        <v>0.09055390101698346</v>
       </c>
       <c r="T7">
-        <v>1.024454130977314</v>
+        <v>1.033577390692459</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>66.17438227776199</v>
+        <v>55.14531856480166</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08762560695596444</v>
+        <v>0.08751284323417709</v>
       </c>
       <c r="C8">
-        <v>28.90693448818092</v>
+        <v>28.62301682804977</v>
       </c>
       <c r="D8">
-        <v>24.45693448818092</v>
+        <v>24.48801682804977</v>
       </c>
       <c r="E8">
-        <v>-17.81</v>
+        <v>-17.495</v>
       </c>
       <c r="F8">
-        <v>1.89</v>
+        <v>2.205</v>
       </c>
       <c r="G8">
         <v>6.34</v>
@@ -1937,28 +1937,28 @@
         <v>5.2425</v>
       </c>
       <c r="M8">
-        <v>0.09506699999999998</v>
+        <v>0.1109115</v>
       </c>
       <c r="N8">
-        <v>5.147432999999999</v>
+        <v>5.131588499999999</v>
       </c>
       <c r="O8">
-        <v>0.87506361</v>
+        <v>0.8723700449999999</v>
       </c>
       <c r="P8">
-        <v>4.27236939</v>
+        <v>4.259218454999999</v>
       </c>
       <c r="Q8">
-        <v>6.34236939</v>
+        <v>6.329218454999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09055390101698346</v>
+        <v>0.09095743358513665</v>
       </c>
       <c r="T8">
-        <v>1.033577390692459</v>
+        <v>1.042896849541262</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>55.14531856480167</v>
+        <v>47.26741591268714</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08751284323417709</v>
+        <v>0.08740007951238972</v>
       </c>
       <c r="C9">
-        <v>28.62301682804976</v>
+        <v>28.33917827360106</v>
       </c>
       <c r="D9">
-        <v>24.48801682804977</v>
+        <v>24.51917827360106</v>
       </c>
       <c r="E9">
-        <v>-17.495</v>
+        <v>-17.18</v>
       </c>
       <c r="F9">
-        <v>2.205</v>
+        <v>2.52</v>
       </c>
       <c r="G9">
         <v>6.34</v>
@@ -2019,28 +2019,28 @@
         <v>5.2425</v>
       </c>
       <c r="M9">
-        <v>0.1109115</v>
+        <v>0.126756</v>
       </c>
       <c r="N9">
-        <v>5.131588499999999</v>
+        <v>5.115743999999999</v>
       </c>
       <c r="O9">
-        <v>0.8723700449999999</v>
+        <v>0.86967648</v>
       </c>
       <c r="P9">
-        <v>4.259218454999999</v>
+        <v>4.24606752</v>
       </c>
       <c r="Q9">
-        <v>6.329218454999999</v>
+        <v>6.316067519999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09095743358513665</v>
+        <v>0.09136973860042361</v>
       </c>
       <c r="T9">
-        <v>1.042896849541262</v>
+        <v>1.052418905321561</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.26741591268714</v>
+        <v>41.35898892360125</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08740007951238972</v>
+        <v>0.08728731579060235</v>
       </c>
       <c r="C10">
-        <v>28.33917827360106</v>
+        <v>28.05541912720983</v>
       </c>
       <c r="D10">
-        <v>24.51917827360106</v>
+        <v>24.55041912720983</v>
       </c>
       <c r="E10">
-        <v>-17.18</v>
+        <v>-16.865</v>
       </c>
       <c r="F10">
-        <v>2.52</v>
+        <v>2.835</v>
       </c>
       <c r="G10">
         <v>6.34</v>
@@ -2101,28 +2101,28 @@
         <v>5.2425</v>
       </c>
       <c r="M10">
-        <v>0.126756</v>
+        <v>0.1426005</v>
       </c>
       <c r="N10">
-        <v>5.115743999999999</v>
+        <v>5.099899499999999</v>
       </c>
       <c r="O10">
-        <v>0.86967648</v>
+        <v>0.8669829149999999</v>
       </c>
       <c r="P10">
-        <v>4.24606752</v>
+        <v>4.232916585</v>
       </c>
       <c r="Q10">
-        <v>6.316067519999999</v>
+        <v>6.302916585</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09136973860042361</v>
+        <v>0.09179110526439818</v>
       </c>
       <c r="T10">
-        <v>1.052418905321561</v>
+        <v>1.062150237053076</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.35898892360125</v>
+        <v>36.76354570986778</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08728731579060235</v>
+        <v>0.08717455206881497</v>
       </c>
       <c r="C11">
-        <v>28.05541912720983</v>
+        <v>27.77173969279413</v>
       </c>
       <c r="D11">
-        <v>24.55041912720983</v>
+        <v>24.58173969279413</v>
       </c>
       <c r="E11">
-        <v>-16.865</v>
+        <v>-16.55</v>
       </c>
       <c r="F11">
-        <v>2.835</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
         <v>6.34</v>
@@ -2183,28 +2183,28 @@
         <v>5.2425</v>
       </c>
       <c r="M11">
-        <v>0.1426005</v>
+        <v>0.158445</v>
       </c>
       <c r="N11">
-        <v>5.099899499999999</v>
+        <v>5.084054999999999</v>
       </c>
       <c r="O11">
-        <v>0.8669829149999999</v>
+        <v>0.86428935</v>
       </c>
       <c r="P11">
-        <v>4.232916585</v>
+        <v>4.219765649999999</v>
       </c>
       <c r="Q11">
-        <v>6.302916585</v>
+        <v>6.28976565</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09179110526439818</v>
+        <v>0.09222183563201664</v>
       </c>
       <c r="T11">
-        <v>1.062150237053076</v>
+        <v>1.072097820600846</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.76354570986778</v>
+        <v>33.087191138881</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08717455206881497</v>
+        <v>0.0870617883470276</v>
       </c>
       <c r="C12">
-        <v>27.77173969279413</v>
+        <v>27.48814027582491</v>
       </c>
       <c r="D12">
-        <v>24.58173969279413</v>
+        <v>24.61314027582491</v>
       </c>
       <c r="E12">
-        <v>-16.55</v>
+        <v>-16.235</v>
       </c>
       <c r="F12">
-        <v>3.15</v>
+        <v>3.465</v>
       </c>
       <c r="G12">
         <v>6.34</v>
@@ -2265,28 +2265,28 @@
         <v>5.2425</v>
       </c>
       <c r="M12">
-        <v>0.158445</v>
+        <v>0.1742895</v>
       </c>
       <c r="N12">
-        <v>5.084054999999999</v>
+        <v>5.068210499999999</v>
       </c>
       <c r="O12">
-        <v>0.86428935</v>
+        <v>0.8615957849999999</v>
       </c>
       <c r="P12">
-        <v>4.219765649999999</v>
+        <v>4.206614715</v>
       </c>
       <c r="Q12">
-        <v>6.28976565</v>
+        <v>6.276614714999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09222183563201664</v>
+        <v>0.09266224533373887</v>
       </c>
       <c r="T12">
-        <v>1.072097820600846</v>
+        <v>1.082268945351937</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.087191138881</v>
+        <v>30.07926467171</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0870617883470276</v>
+        <v>0.08694902462524022</v>
       </c>
       <c r="C13">
-        <v>27.48814027582491</v>
+        <v>27.20462118333596</v>
       </c>
       <c r="D13">
-        <v>24.61314027582491</v>
+        <v>24.64462118333596</v>
       </c>
       <c r="E13">
-        <v>-16.235</v>
+        <v>-15.92</v>
       </c>
       <c r="F13">
-        <v>3.465</v>
+        <v>3.78</v>
       </c>
       <c r="G13">
         <v>6.34</v>
@@ -2347,28 +2347,28 @@
         <v>5.2425</v>
       </c>
       <c r="M13">
-        <v>0.1742895</v>
+        <v>0.190134</v>
       </c>
       <c r="N13">
-        <v>5.068210499999999</v>
+        <v>5.052366</v>
       </c>
       <c r="O13">
-        <v>0.8615957849999999</v>
+        <v>0.85890222</v>
       </c>
       <c r="P13">
-        <v>4.206614715</v>
+        <v>4.19346378</v>
       </c>
       <c r="Q13">
-        <v>6.276614714999999</v>
+        <v>6.26346378</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09266224533373887</v>
+        <v>0.0931126643468639</v>
       </c>
       <c r="T13">
-        <v>1.082268945351937</v>
+        <v>1.092671232029189</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.07926467171</v>
+        <v>27.57265928240084</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08694902462524022</v>
+        <v>0.08683626090345285</v>
       </c>
       <c r="C14">
-        <v>27.20462118333596</v>
+        <v>26.92118272393389</v>
       </c>
       <c r="D14">
-        <v>24.64462118333596</v>
+        <v>24.67618272393388</v>
       </c>
       <c r="E14">
-        <v>-15.92</v>
+        <v>-15.605</v>
       </c>
       <c r="F14">
-        <v>3.78</v>
+        <v>4.095</v>
       </c>
       <c r="G14">
         <v>6.34</v>
@@ -2429,28 +2429,28 @@
         <v>5.2425</v>
       </c>
       <c r="M14">
-        <v>0.190134</v>
+        <v>0.2059785</v>
       </c>
       <c r="N14">
-        <v>5.052366</v>
+        <v>5.0365215</v>
       </c>
       <c r="O14">
-        <v>0.85890222</v>
+        <v>0.8562086550000001</v>
       </c>
       <c r="P14">
-        <v>4.19346378</v>
+        <v>4.180312845</v>
       </c>
       <c r="Q14">
-        <v>6.26346378</v>
+        <v>6.250312845</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0931126643468639</v>
+        <v>0.09357343782006075</v>
       </c>
       <c r="T14">
-        <v>1.092671232029189</v>
+        <v>1.103312651733505</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.57265928240084</v>
+        <v>25.45168549144693</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08683626090345285</v>
+        <v>0.08672349718166548</v>
       </c>
       <c r="C15">
-        <v>26.92118272393389</v>
+        <v>26.63782520780821</v>
       </c>
       <c r="D15">
-        <v>24.67618272393388</v>
+        <v>24.70782520780821</v>
       </c>
       <c r="E15">
-        <v>-15.605</v>
+        <v>-15.29</v>
       </c>
       <c r="F15">
-        <v>4.095</v>
+        <v>4.41</v>
       </c>
       <c r="G15">
         <v>6.34</v>
@@ -2511,28 +2511,28 @@
         <v>5.2425</v>
       </c>
       <c r="M15">
-        <v>0.2059785</v>
+        <v>0.221823</v>
       </c>
       <c r="N15">
-        <v>5.0365215</v>
+        <v>5.020677</v>
       </c>
       <c r="O15">
-        <v>0.8562086550000001</v>
+        <v>0.85351509</v>
       </c>
       <c r="P15">
-        <v>4.180312845</v>
+        <v>4.16716191</v>
       </c>
       <c r="Q15">
-        <v>6.250312845</v>
+        <v>6.237161909999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09357343782006075</v>
+        <v>0.09404492695542499</v>
       </c>
       <c r="T15">
-        <v>1.103312651733505</v>
+        <v>1.114201546314665</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.45168549144693</v>
+        <v>23.63370795634357</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08672349718166548</v>
+        <v>0.08661073345987812</v>
       </c>
       <c r="C16">
-        <v>26.63782520780821</v>
+        <v>26.35454894674155</v>
       </c>
       <c r="D16">
-        <v>24.70782520780821</v>
+        <v>24.73954894674155</v>
       </c>
       <c r="E16">
-        <v>-15.29</v>
+        <v>-14.975</v>
       </c>
       <c r="F16">
-        <v>4.41</v>
+        <v>4.725000000000001</v>
       </c>
       <c r="G16">
         <v>6.34</v>
@@ -2593,28 +2593,28 @@
         <v>5.2425</v>
       </c>
       <c r="M16">
-        <v>0.221823</v>
+        <v>0.2376675</v>
       </c>
       <c r="N16">
-        <v>5.020677</v>
+        <v>5.0048325</v>
       </c>
       <c r="O16">
-        <v>0.85351509</v>
+        <v>0.8508215250000001</v>
       </c>
       <c r="P16">
-        <v>4.16716191</v>
+        <v>4.154010975</v>
       </c>
       <c r="Q16">
-        <v>6.237161909999999</v>
+        <v>6.224010975000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09404492695542499</v>
+        <v>0.09452750995279779</v>
       </c>
       <c r="T16">
-        <v>1.114201546314665</v>
+        <v>1.125346650180088</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.63370795634357</v>
+        <v>22.05812742592067</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08661073345987812</v>
+        <v>0.08649796973809074</v>
       </c>
       <c r="C17">
-        <v>26.35454894674155</v>
+        <v>26.07135425411983</v>
       </c>
       <c r="D17">
-        <v>24.73954894674155</v>
+        <v>24.77135425411982</v>
       </c>
       <c r="E17">
-        <v>-14.975</v>
+        <v>-14.66</v>
       </c>
       <c r="F17">
-        <v>4.725</v>
+        <v>5.04</v>
       </c>
       <c r="G17">
         <v>6.34</v>
@@ -2675,28 +2675,28 @@
         <v>5.2425</v>
       </c>
       <c r="M17">
-        <v>0.2376675</v>
+        <v>0.253512</v>
       </c>
       <c r="N17">
-        <v>5.0048325</v>
+        <v>4.988988</v>
       </c>
       <c r="O17">
-        <v>0.8508215250000001</v>
+        <v>0.84812796</v>
       </c>
       <c r="P17">
-        <v>4.154010975</v>
+        <v>4.14086004</v>
       </c>
       <c r="Q17">
-        <v>6.224010975000001</v>
+        <v>6.21086004</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09452750995279779</v>
+        <v>0.0950215830215366</v>
       </c>
       <c r="T17">
-        <v>1.125346650180088</v>
+        <v>1.136757113661353</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.05812742592067</v>
+        <v>20.67949446180062</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08649796973809074</v>
+        <v>0.08638520601630338</v>
       </c>
       <c r="C18">
-        <v>26.07135425411983</v>
+        <v>25.78824144494259</v>
       </c>
       <c r="D18">
-        <v>24.77135425411982</v>
+        <v>24.80324144494259</v>
       </c>
       <c r="E18">
-        <v>-14.66</v>
+        <v>-14.345</v>
       </c>
       <c r="F18">
-        <v>5.04</v>
+        <v>5.355</v>
       </c>
       <c r="G18">
         <v>6.34</v>
@@ -2757,28 +2757,28 @@
         <v>5.2425</v>
       </c>
       <c r="M18">
-        <v>0.253512</v>
+        <v>0.2693565</v>
       </c>
       <c r="N18">
-        <v>4.988988</v>
+        <v>4.9731435</v>
       </c>
       <c r="O18">
-        <v>0.84812796</v>
+        <v>0.8454343950000001</v>
       </c>
       <c r="P18">
-        <v>4.14086004</v>
+        <v>4.127709105</v>
       </c>
       <c r="Q18">
-        <v>6.21086004</v>
+        <v>6.197709104999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0950215830215366</v>
+        <v>0.09552756146542576</v>
       </c>
       <c r="T18">
-        <v>1.136757113661353</v>
+        <v>1.148442528069879</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.67949446180062</v>
+        <v>19.46305361110647</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08638520601630338</v>
+        <v>0.08627244229451601</v>
       </c>
       <c r="C19">
-        <v>25.78824144494259</v>
+        <v>25.50521083583344</v>
       </c>
       <c r="D19">
-        <v>24.80324144494259</v>
+        <v>24.83521083583344</v>
       </c>
       <c r="E19">
-        <v>-14.345</v>
+        <v>-14.03</v>
       </c>
       <c r="F19">
-        <v>5.355</v>
+        <v>5.670000000000001</v>
       </c>
       <c r="G19">
         <v>6.34</v>
@@ -2839,28 +2839,28 @@
         <v>5.2425</v>
       </c>
       <c r="M19">
-        <v>0.2693565</v>
+        <v>0.285201</v>
       </c>
       <c r="N19">
-        <v>4.9731435</v>
+        <v>4.957299</v>
       </c>
       <c r="O19">
-        <v>0.8454343950000001</v>
+        <v>0.84274083</v>
       </c>
       <c r="P19">
-        <v>4.127709105</v>
+        <v>4.11455817</v>
       </c>
       <c r="Q19">
-        <v>6.197709104999999</v>
+        <v>6.184558169999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09552756146542576</v>
+        <v>0.09604588084697074</v>
       </c>
       <c r="T19">
-        <v>1.148442528069879</v>
+        <v>1.160412952585929</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.46305361110647</v>
+        <v>18.38177285493389</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08627244229451603</v>
+        <v>0.08615967857272863</v>
       </c>
       <c r="C20">
-        <v>25.50521083583344</v>
+        <v>25.22226274505051</v>
       </c>
       <c r="D20">
-        <v>24.83521083583344</v>
+        <v>24.86726274505051</v>
       </c>
       <c r="E20">
-        <v>-14.03</v>
+        <v>-13.715</v>
       </c>
       <c r="F20">
-        <v>5.67</v>
+        <v>5.985</v>
       </c>
       <c r="G20">
         <v>6.34</v>
@@ -2921,28 +2921,28 @@
         <v>5.2425</v>
       </c>
       <c r="M20">
-        <v>0.285201</v>
+        <v>0.3010455</v>
       </c>
       <c r="N20">
-        <v>4.957299</v>
+        <v>4.9414545</v>
       </c>
       <c r="O20">
-        <v>0.84274083</v>
+        <v>0.840047265</v>
       </c>
       <c r="P20">
-        <v>4.11455817</v>
+        <v>4.101407235</v>
       </c>
       <c r="Q20">
-        <v>6.184558169999999</v>
+        <v>6.171407235</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09604588084697074</v>
+        <v>0.09657699823793658</v>
       </c>
       <c r="T20">
-        <v>1.160412952585929</v>
+        <v>1.172678943139413</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.38177285493389</v>
+        <v>17.41431112572684</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08615967857272863</v>
+        <v>0.08604691485094128</v>
       </c>
       <c r="C21">
-        <v>25.22226274505051</v>
+        <v>24.93939749249696</v>
       </c>
       <c r="D21">
-        <v>24.86726274505051</v>
+        <v>24.89939749249696</v>
       </c>
       <c r="E21">
-        <v>-13.715</v>
+        <v>-13.4</v>
       </c>
       <c r="F21">
-        <v>5.985</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="G21">
         <v>6.34</v>
@@ -3003,28 +3003,28 @@
         <v>5.2425</v>
       </c>
       <c r="M21">
-        <v>0.3010455</v>
+        <v>0.31689</v>
       </c>
       <c r="N21">
-        <v>4.9414545</v>
+        <v>4.92561</v>
       </c>
       <c r="O21">
-        <v>0.840047265</v>
+        <v>0.8373537</v>
       </c>
       <c r="P21">
-        <v>4.101407235</v>
+        <v>4.088256299999999</v>
       </c>
       <c r="Q21">
-        <v>6.171407235</v>
+        <v>6.1582563</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09657699823793658</v>
+        <v>0.09712139356367658</v>
       </c>
       <c r="T21">
-        <v>1.172678943139413</v>
+        <v>1.185251583456734</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.41431112572684</v>
+        <v>16.5435955694405</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08604691485094128</v>
+        <v>0.08593415112915391</v>
       </c>
       <c r="C22">
-        <v>24.93939749249696</v>
+        <v>24.65661539973173</v>
       </c>
       <c r="D22">
-        <v>24.89939749249696</v>
+        <v>24.93161539973173</v>
       </c>
       <c r="E22">
-        <v>-13.4</v>
+        <v>-13.085</v>
       </c>
       <c r="F22">
-        <v>6.300000000000001</v>
+        <v>6.615</v>
       </c>
       <c r="G22">
         <v>6.34</v>
@@ -3085,28 +3085,28 @@
         <v>5.2425</v>
       </c>
       <c r="M22">
-        <v>0.31689</v>
+        <v>0.3327345</v>
       </c>
       <c r="N22">
-        <v>4.92561</v>
+        <v>4.9097655</v>
       </c>
       <c r="O22">
-        <v>0.8373537</v>
+        <v>0.834660135</v>
       </c>
       <c r="P22">
-        <v>4.088256299999999</v>
+        <v>4.075105365</v>
       </c>
       <c r="Q22">
-        <v>6.1582563</v>
+        <v>6.145105364999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09712139356367658</v>
+        <v>0.0976795710495619</v>
       </c>
       <c r="T22">
-        <v>1.185251583456734</v>
+        <v>1.198142518465633</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.5435955694405</v>
+        <v>15.75580530422905</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08593415112915391</v>
+        <v>0.08582138740736653</v>
       </c>
       <c r="C23">
-        <v>24.65661539973173</v>
+        <v>24.37391678998016</v>
       </c>
       <c r="D23">
-        <v>24.93161539973173</v>
+        <v>24.96391678998016</v>
       </c>
       <c r="E23">
-        <v>-13.085</v>
+        <v>-12.77</v>
       </c>
       <c r="F23">
-        <v>6.614999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="G23">
         <v>6.34</v>
@@ -3167,28 +3167,28 @@
         <v>5.2425</v>
       </c>
       <c r="M23">
-        <v>0.3327344999999999</v>
+        <v>0.348579</v>
       </c>
       <c r="N23">
-        <v>4.9097655</v>
+        <v>4.893921</v>
       </c>
       <c r="O23">
-        <v>0.834660135</v>
+        <v>0.83196657</v>
       </c>
       <c r="P23">
-        <v>4.075105365</v>
+        <v>4.06195443</v>
       </c>
       <c r="Q23">
-        <v>6.145105364999999</v>
+        <v>6.13195443</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0976795710495619</v>
+        <v>0.09825206077867503</v>
       </c>
       <c r="T23">
-        <v>1.198142518465633</v>
+        <v>1.211363990269631</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.75580530422905</v>
+        <v>15.039632335855</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08582138740736653</v>
+        <v>0.08570862368557915</v>
       </c>
       <c r="C24">
-        <v>24.37391678998016</v>
+        <v>24.09130198814488</v>
       </c>
       <c r="D24">
-        <v>24.96391678998016</v>
+        <v>24.99630198814488</v>
       </c>
       <c r="E24">
-        <v>-12.77</v>
+        <v>-12.455</v>
       </c>
       <c r="F24">
-        <v>6.93</v>
+        <v>7.245</v>
       </c>
       <c r="G24">
         <v>6.34</v>
@@ -3249,28 +3249,28 @@
         <v>5.2425</v>
       </c>
       <c r="M24">
-        <v>0.348579</v>
+        <v>0.3644235</v>
       </c>
       <c r="N24">
-        <v>4.893921</v>
+        <v>4.8780765</v>
       </c>
       <c r="O24">
-        <v>0.83196657</v>
+        <v>0.829273005</v>
       </c>
       <c r="P24">
-        <v>4.06195443</v>
+        <v>4.048803495</v>
       </c>
       <c r="Q24">
-        <v>6.13195443</v>
+        <v>6.118803495</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09825206077867503</v>
+        <v>0.09883942037088202</v>
       </c>
       <c r="T24">
-        <v>1.211363990269631</v>
+        <v>1.224928876925682</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.039632335855</v>
+        <v>14.38573527777435</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08570862368557915</v>
+        <v>0.08559585996379179</v>
       </c>
       <c r="C25">
-        <v>24.09130198814488</v>
+        <v>23.80877132081663</v>
       </c>
       <c r="D25">
-        <v>24.99630198814488</v>
+        <v>25.02877132081663</v>
       </c>
       <c r="E25">
-        <v>-12.455</v>
+        <v>-12.14</v>
       </c>
       <c r="F25">
-        <v>7.245</v>
+        <v>7.56</v>
       </c>
       <c r="G25">
         <v>6.34</v>
@@ -3331,28 +3331,28 @@
         <v>5.2425</v>
       </c>
       <c r="M25">
-        <v>0.3644235</v>
+        <v>0.380268</v>
       </c>
       <c r="N25">
-        <v>4.8780765</v>
+        <v>4.862232</v>
       </c>
       <c r="O25">
-        <v>0.829273005</v>
+        <v>0.8265794400000001</v>
       </c>
       <c r="P25">
-        <v>4.048803495</v>
+        <v>4.03565256</v>
       </c>
       <c r="Q25">
-        <v>6.118803495</v>
+        <v>6.105652559999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09883942037088202</v>
+        <v>0.09944223679446287</v>
       </c>
       <c r="T25">
-        <v>1.224928876925682</v>
+        <v>1.238850734283207</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.38573527777435</v>
+        <v>13.78632964120042</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08559585996379179</v>
+        <v>0.08548309624200441</v>
       </c>
       <c r="C26">
-        <v>23.80877132081664</v>
+        <v>23.52632511628533</v>
       </c>
       <c r="D26">
-        <v>25.02877132081663</v>
+        <v>25.06132511628533</v>
       </c>
       <c r="E26">
-        <v>-12.14</v>
+        <v>-11.825</v>
       </c>
       <c r="F26">
-        <v>7.56</v>
+        <v>7.875</v>
       </c>
       <c r="G26">
         <v>6.34</v>
@@ -3413,28 +3413,28 @@
         <v>5.2425</v>
       </c>
       <c r="M26">
-        <v>0.3802679999999999</v>
+        <v>0.3961125</v>
       </c>
       <c r="N26">
-        <v>4.862232</v>
+        <v>4.8463875</v>
       </c>
       <c r="O26">
-        <v>0.8265794400000001</v>
+        <v>0.823885875</v>
       </c>
       <c r="P26">
-        <v>4.03565256</v>
+        <v>4.022501624999999</v>
       </c>
       <c r="Q26">
-        <v>6.105652559999999</v>
+        <v>6.092501624999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09944223679446287</v>
+        <v>0.1000611283226726</v>
       </c>
       <c r="T26">
-        <v>1.238850734283207</v>
+        <v>1.253143841170267</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.78632964120042</v>
+        <v>13.2348764555524</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08548309624200441</v>
+        <v>0.08569403252021704</v>
       </c>
       <c r="C27">
-        <v>23.52632511628533</v>
+        <v>23.15049864134075</v>
       </c>
       <c r="D27">
-        <v>25.06132511628533</v>
+        <v>25.00049864134075</v>
       </c>
       <c r="E27">
-        <v>-11.825</v>
+        <v>-11.51</v>
       </c>
       <c r="F27">
-        <v>7.875</v>
+        <v>8.19</v>
       </c>
       <c r="G27">
         <v>6.34</v>
@@ -3495,45 +3495,45 @@
         <v>5.2425</v>
       </c>
       <c r="M27">
-        <v>0.3961125</v>
+        <v>0.424242</v>
       </c>
       <c r="N27">
-        <v>4.8463875</v>
+        <v>4.818258</v>
       </c>
       <c r="O27">
-        <v>0.823885875</v>
+        <v>0.8191038600000001</v>
       </c>
       <c r="P27">
-        <v>4.022501624999999</v>
+        <v>3.99915414</v>
       </c>
       <c r="Q27">
-        <v>6.092501624999999</v>
+        <v>6.06915414</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1000611283226726</v>
+        <v>0.1006967466489419</v>
       </c>
       <c r="T27">
-        <v>1.253143841170267</v>
+        <v>1.267823248243463</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.17</v>
       </c>
       <c r="W27">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.2348764555524</v>
+        <v>12.35733378590522</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08569403252021704</v>
+        <v>0.08559371879842967</v>
       </c>
       <c r="C28">
-        <v>23.15049864134075</v>
+        <v>22.86438866683287</v>
       </c>
       <c r="D28">
-        <v>25.00049864134075</v>
+        <v>25.02938866683287</v>
       </c>
       <c r="E28">
-        <v>-11.51</v>
+        <v>-11.195</v>
       </c>
       <c r="F28">
-        <v>8.19</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="G28">
         <v>6.34</v>
@@ -3577,28 +3577,28 @@
         <v>5.2425</v>
       </c>
       <c r="M28">
-        <v>0.424242</v>
+        <v>0.440559</v>
       </c>
       <c r="N28">
-        <v>4.818258</v>
+        <v>4.801940999999999</v>
       </c>
       <c r="O28">
-        <v>0.8191038600000001</v>
+        <v>0.81632997</v>
       </c>
       <c r="P28">
-        <v>3.99915414</v>
+        <v>3.985611029999999</v>
       </c>
       <c r="Q28">
-        <v>6.06915414</v>
+        <v>6.05561103</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1006967466489419</v>
+        <v>0.101349779175931</v>
       </c>
       <c r="T28">
-        <v>1.267823248243463</v>
+        <v>1.282904830852911</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.35733378590522</v>
+        <v>11.89965475679761</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08559371879842967</v>
+        <v>0.0854934050766423</v>
       </c>
       <c r="C29">
-        <v>22.86438866683287</v>
+        <v>22.57834553892554</v>
       </c>
       <c r="D29">
-        <v>25.02938866683287</v>
+        <v>25.05834553892554</v>
       </c>
       <c r="E29">
-        <v>-11.195</v>
+        <v>-10.88</v>
       </c>
       <c r="F29">
-        <v>8.505000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G29">
         <v>6.34</v>
@@ -3659,28 +3659,28 @@
         <v>5.2425</v>
       </c>
       <c r="M29">
-        <v>0.440559</v>
+        <v>0.456876</v>
       </c>
       <c r="N29">
-        <v>4.801940999999999</v>
+        <v>4.785623999999999</v>
       </c>
       <c r="O29">
-        <v>0.81632997</v>
+        <v>0.81355608</v>
       </c>
       <c r="P29">
-        <v>3.985611029999999</v>
+        <v>3.972067919999999</v>
       </c>
       <c r="Q29">
-        <v>6.05561103</v>
+        <v>6.042067919999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.101349779175931</v>
+        <v>0.1020209514953365</v>
       </c>
       <c r="T29">
-        <v>1.282904830852911</v>
+        <v>1.298405346312622</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.89965475679761</v>
+        <v>11.47466708691198</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0854934050766423</v>
+        <v>0.08539309135485493</v>
       </c>
       <c r="C30">
-        <v>22.57834553892554</v>
+        <v>22.29236948989493</v>
       </c>
       <c r="D30">
-        <v>25.05834553892554</v>
+        <v>25.08736948989494</v>
       </c>
       <c r="E30">
-        <v>-10.88</v>
+        <v>-10.565</v>
       </c>
       <c r="F30">
-        <v>8.82</v>
+        <v>9.135000000000002</v>
       </c>
       <c r="G30">
         <v>6.34</v>
@@ -3741,28 +3741,28 @@
         <v>5.2425</v>
       </c>
       <c r="M30">
-        <v>0.456876</v>
+        <v>0.4731930000000001</v>
       </c>
       <c r="N30">
-        <v>4.785623999999999</v>
+        <v>4.769307</v>
       </c>
       <c r="O30">
-        <v>0.81355608</v>
+        <v>0.81078219</v>
       </c>
       <c r="P30">
-        <v>3.972067919999999</v>
+        <v>3.95852481</v>
       </c>
       <c r="Q30">
-        <v>6.042067919999999</v>
+        <v>6.02852481</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1020209514953365</v>
+        <v>0.1027110300772605</v>
       </c>
       <c r="T30">
-        <v>1.298405346312622</v>
+        <v>1.314342496010634</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.47466708691198</v>
+        <v>11.07898891150122</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08539309135485491</v>
+        <v>0.08529277763306756</v>
       </c>
       <c r="C31">
-        <v>22.29236948989494</v>
+        <v>22.00646075309467</v>
       </c>
       <c r="D31">
-        <v>25.08736948989494</v>
+        <v>25.11646075309467</v>
       </c>
       <c r="E31">
-        <v>-10.565</v>
+        <v>-10.25</v>
       </c>
       <c r="F31">
-        <v>9.135</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G31">
         <v>6.34</v>
@@ -3823,28 +3823,28 @@
         <v>5.2425</v>
       </c>
       <c r="M31">
-        <v>0.473193</v>
+        <v>0.4895099999999999</v>
       </c>
       <c r="N31">
-        <v>4.769307</v>
+        <v>4.75299</v>
       </c>
       <c r="O31">
-        <v>0.81078219</v>
+        <v>0.8080083</v>
       </c>
       <c r="P31">
-        <v>3.95852481</v>
+        <v>3.9449817</v>
       </c>
       <c r="Q31">
-        <v>6.02852481</v>
+        <v>6.0149817</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1027110300772605</v>
+        <v>0.1034208251900965</v>
       </c>
       <c r="T31">
-        <v>1.314342496010634</v>
+        <v>1.330734992842876</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.07898891150123</v>
+        <v>10.70968928111785</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08529277763306756</v>
+        <v>0.08519246391128019</v>
       </c>
       <c r="C32">
-        <v>22.00646075309467</v>
+        <v>21.72061956296197</v>
       </c>
       <c r="D32">
-        <v>25.11646075309467</v>
+        <v>25.14561956296197</v>
       </c>
       <c r="E32">
-        <v>-10.25</v>
+        <v>-9.934999999999999</v>
       </c>
       <c r="F32">
-        <v>9.449999999999999</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="G32">
         <v>6.34</v>
@@ -3905,28 +3905,28 @@
         <v>5.2425</v>
       </c>
       <c r="M32">
-        <v>0.4895099999999999</v>
+        <v>0.505827</v>
       </c>
       <c r="N32">
-        <v>4.75299</v>
+        <v>4.736673</v>
       </c>
       <c r="O32">
-        <v>0.8080083</v>
+        <v>0.80523441</v>
       </c>
       <c r="P32">
-        <v>3.9449817</v>
+        <v>3.93143859</v>
       </c>
       <c r="Q32">
-        <v>6.0149817</v>
+        <v>6.001438589999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1034208251900965</v>
+        <v>0.1041511940743191</v>
       </c>
       <c r="T32">
-        <v>1.330734992842876</v>
+        <v>1.347602634510834</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.70968928111785</v>
+        <v>10.36421543333986</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08519246391128019</v>
+        <v>0.08509215018949282</v>
       </c>
       <c r="C33">
-        <v>21.72061956296197</v>
+        <v>21.434846155024</v>
       </c>
       <c r="D33">
-        <v>25.14561956296197</v>
+        <v>25.174846155024</v>
       </c>
       <c r="E33">
-        <v>-9.934999999999999</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="F33">
-        <v>9.765000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="G33">
         <v>6.34</v>
@@ -3987,28 +3987,28 @@
         <v>5.2425</v>
       </c>
       <c r="M33">
-        <v>0.505827</v>
+        <v>0.5221439999999999</v>
       </c>
       <c r="N33">
-        <v>4.736673</v>
+        <v>4.720356</v>
       </c>
       <c r="O33">
-        <v>0.80523441</v>
+        <v>0.80246052</v>
       </c>
       <c r="P33">
-        <v>3.93143859</v>
+        <v>3.91789548</v>
       </c>
       <c r="Q33">
-        <v>6.001438589999999</v>
+        <v>5.98789548</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1041511940743191</v>
+        <v>0.104903044396313</v>
       </c>
       <c r="T33">
-        <v>1.347602634510834</v>
+        <v>1.364966383286674</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.36421543333986</v>
+        <v>10.04033370104799</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08509215018949282</v>
+        <v>0.08545746646770544</v>
       </c>
       <c r="C34">
-        <v>21.434846155024</v>
+        <v>21.01373599861014</v>
       </c>
       <c r="D34">
-        <v>25.174846155024</v>
+        <v>25.06873599861014</v>
       </c>
       <c r="E34">
-        <v>-9.619999999999999</v>
+        <v>-9.304999999999998</v>
       </c>
       <c r="F34">
-        <v>10.08</v>
+        <v>10.395</v>
       </c>
       <c r="G34">
         <v>6.34</v>
@@ -4069,45 +4069,45 @@
         <v>5.2425</v>
       </c>
       <c r="M34">
-        <v>0.5221439999999999</v>
+        <v>0.5561325</v>
       </c>
       <c r="N34">
-        <v>4.720356</v>
+        <v>4.686367499999999</v>
       </c>
       <c r="O34">
-        <v>0.80246052</v>
+        <v>0.796682475</v>
       </c>
       <c r="P34">
-        <v>3.91789548</v>
+        <v>3.889685024999999</v>
       </c>
       <c r="Q34">
-        <v>5.98789548</v>
+        <v>5.959685024999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.104903044396313</v>
+        <v>0.1056773380115007</v>
       </c>
       <c r="T34">
-        <v>1.364966383286674</v>
+        <v>1.382848452921493</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.17</v>
       </c>
       <c r="W34">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>10.04033370104799</v>
+        <v>9.4267103612898</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08545746646770544</v>
+        <v>0.08537126274591807</v>
       </c>
       <c r="C35">
-        <v>21.01373599861014</v>
+        <v>20.72369411015043</v>
       </c>
       <c r="D35">
-        <v>25.06873599861014</v>
+        <v>25.09369411015043</v>
       </c>
       <c r="E35">
-        <v>-9.304999999999998</v>
+        <v>-8.989999999999998</v>
       </c>
       <c r="F35">
-        <v>10.395</v>
+        <v>10.71</v>
       </c>
       <c r="G35">
         <v>6.34</v>
@@ -4151,28 +4151,28 @@
         <v>5.2425</v>
       </c>
       <c r="M35">
-        <v>0.5561325</v>
+        <v>0.5729850000000001</v>
       </c>
       <c r="N35">
-        <v>4.686367499999999</v>
+        <v>4.669515</v>
       </c>
       <c r="O35">
-        <v>0.796682475</v>
+        <v>0.79381755</v>
       </c>
       <c r="P35">
-        <v>3.889685024999999</v>
+        <v>3.87569745</v>
       </c>
       <c r="Q35">
-        <v>5.959685024999999</v>
+        <v>5.945697449999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1056773380115007</v>
+        <v>0.1064750950695728</v>
       </c>
       <c r="T35">
-        <v>1.382848452921493</v>
+        <v>1.401272403454338</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.4267103612898</v>
+        <v>9.149454174193039</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08537126274591807</v>
+        <v>0.08528505902413071</v>
       </c>
       <c r="C36">
-        <v>20.72369411015043</v>
+        <v>20.43370196716717</v>
       </c>
       <c r="D36">
-        <v>25.09369411015043</v>
+        <v>25.11870196716718</v>
       </c>
       <c r="E36">
-        <v>-8.989999999999998</v>
+        <v>-8.674999999999999</v>
       </c>
       <c r="F36">
-        <v>10.71</v>
+        <v>11.025</v>
       </c>
       <c r="G36">
         <v>6.34</v>
@@ -4233,28 +4233,28 @@
         <v>5.2425</v>
       </c>
       <c r="M36">
-        <v>0.5729850000000001</v>
+        <v>0.5898375</v>
       </c>
       <c r="N36">
-        <v>4.669515</v>
+        <v>4.6526625</v>
       </c>
       <c r="O36">
-        <v>0.79381755</v>
+        <v>0.7909526250000001</v>
       </c>
       <c r="P36">
-        <v>3.87569745</v>
+        <v>3.861709875</v>
       </c>
       <c r="Q36">
-        <v>5.945697449999999</v>
+        <v>5.931709874999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1064750950695728</v>
+        <v>0.1072973984986626</v>
       </c>
       <c r="T36">
-        <v>1.401272403454338</v>
+        <v>1.420263244772809</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.149454174193039</v>
+        <v>8.888041197787526</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08528505902413071</v>
+        <v>0.08519885530234333</v>
       </c>
       <c r="C37">
-        <v>20.43370196716717</v>
+        <v>20.14375971853469</v>
       </c>
       <c r="D37">
-        <v>25.11870196716718</v>
+        <v>25.14375971853469</v>
       </c>
       <c r="E37">
-        <v>-8.674999999999999</v>
+        <v>-8.359999999999998</v>
       </c>
       <c r="F37">
-        <v>11.025</v>
+        <v>11.34</v>
       </c>
       <c r="G37">
         <v>6.34</v>
@@ -4315,28 +4315,28 @@
         <v>5.2425</v>
       </c>
       <c r="M37">
-        <v>0.5898375</v>
+        <v>0.6066900000000001</v>
       </c>
       <c r="N37">
-        <v>4.6526625</v>
+        <v>4.635809999999999</v>
       </c>
       <c r="O37">
-        <v>0.7909526250000001</v>
+        <v>0.7880876999999999</v>
       </c>
       <c r="P37">
-        <v>3.861709875</v>
+        <v>3.847722299999999</v>
       </c>
       <c r="Q37">
-        <v>5.931709874999999</v>
+        <v>5.917722299999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1072973984986626</v>
+        <v>0.1081453989099115</v>
       </c>
       <c r="T37">
-        <v>1.420263244772809</v>
+        <v>1.439847549882482</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.888041197787526</v>
+        <v>8.641151164515648</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08519885530234332</v>
+        <v>0.08511265158055595</v>
       </c>
       <c r="C38">
-        <v>20.1437597185347</v>
+        <v>19.85386751372193</v>
       </c>
       <c r="D38">
-        <v>25.1437597185347</v>
+        <v>25.16886751372193</v>
       </c>
       <c r="E38">
-        <v>-8.359999999999999</v>
+        <v>-8.045</v>
       </c>
       <c r="F38">
-        <v>11.34</v>
+        <v>11.655</v>
       </c>
       <c r="G38">
         <v>6.34</v>
@@ -4397,28 +4397,28 @@
         <v>5.2425</v>
       </c>
       <c r="M38">
-        <v>0.60669</v>
+        <v>0.6235425</v>
       </c>
       <c r="N38">
-        <v>4.635809999999999</v>
+        <v>4.6189575</v>
       </c>
       <c r="O38">
-        <v>0.7880876999999999</v>
+        <v>0.785222775</v>
       </c>
       <c r="P38">
-        <v>3.847722299999999</v>
+        <v>3.833734724999999</v>
       </c>
       <c r="Q38">
-        <v>5.917722299999999</v>
+        <v>5.903734725</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081453989099115</v>
+        <v>0.1090203199691364</v>
       </c>
       <c r="T38">
-        <v>1.439847549882482</v>
+        <v>1.46005357896389</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.64115116451565</v>
+        <v>8.407606538447659</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08511265158055595</v>
+        <v>0.08502644785876859</v>
       </c>
       <c r="C39">
-        <v>19.85386751372193</v>
+        <v>19.56402550279545</v>
       </c>
       <c r="D39">
-        <v>25.16886751372193</v>
+        <v>25.19402550279545</v>
       </c>
       <c r="E39">
-        <v>-8.045</v>
+        <v>-7.729999999999999</v>
       </c>
       <c r="F39">
-        <v>11.655</v>
+        <v>11.97</v>
       </c>
       <c r="G39">
         <v>6.34</v>
@@ -4479,28 +4479,28 @@
         <v>5.2425</v>
       </c>
       <c r="M39">
-        <v>0.6235425</v>
+        <v>0.640395</v>
       </c>
       <c r="N39">
-        <v>4.6189575</v>
+        <v>4.602105</v>
       </c>
       <c r="O39">
-        <v>0.785222775</v>
+        <v>0.78235785</v>
       </c>
       <c r="P39">
-        <v>3.833734724999999</v>
+        <v>3.81974715</v>
       </c>
       <c r="Q39">
-        <v>5.903734725</v>
+        <v>5.88974715</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1090203199691364</v>
+        <v>0.1099234642883364</v>
       </c>
       <c r="T39">
-        <v>1.46005357896389</v>
+        <v>1.480911415435022</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.407606538447659</v>
+        <v>8.1863537348043</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08502644785876859</v>
+        <v>0.08494024413698122</v>
       </c>
       <c r="C40">
-        <v>19.56402550279545</v>
+        <v>19.27423383642243</v>
       </c>
       <c r="D40">
-        <v>25.19402550279545</v>
+        <v>25.21923383642243</v>
       </c>
       <c r="E40">
-        <v>-7.729999999999999</v>
+        <v>-7.414999999999999</v>
       </c>
       <c r="F40">
-        <v>11.97</v>
+        <v>12.285</v>
       </c>
       <c r="G40">
         <v>6.34</v>
@@ -4561,28 +4561,28 @@
         <v>5.2425</v>
       </c>
       <c r="M40">
-        <v>0.640395</v>
+        <v>0.6572475</v>
       </c>
       <c r="N40">
-        <v>4.602105</v>
+        <v>4.585252499999999</v>
       </c>
       <c r="O40">
-        <v>0.78235785</v>
+        <v>0.7794929249999999</v>
       </c>
       <c r="P40">
-        <v>3.81974715</v>
+        <v>3.805759574999999</v>
       </c>
       <c r="Q40">
-        <v>5.88974715</v>
+        <v>5.875759574999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1099234642883364</v>
+        <v>0.1108562198966905</v>
       </c>
       <c r="T40">
-        <v>1.480911415435022</v>
+        <v>1.50245311539701</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.1863537348043</v>
+        <v>7.976447228783677</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08494024413698122</v>
+        <v>0.08485404041519384</v>
       </c>
       <c r="C41">
-        <v>19.27423383642243</v>
+        <v>18.98449266587367</v>
       </c>
       <c r="D41">
-        <v>25.21923383642243</v>
+        <v>25.24449266587367</v>
       </c>
       <c r="E41">
-        <v>-7.414999999999999</v>
+        <v>-7.099999999999998</v>
       </c>
       <c r="F41">
-        <v>12.285</v>
+        <v>12.6</v>
       </c>
       <c r="G41">
         <v>6.34</v>
@@ -4643,28 +4643,28 @@
         <v>5.2425</v>
       </c>
       <c r="M41">
-        <v>0.6572475</v>
+        <v>0.6741</v>
       </c>
       <c r="N41">
-        <v>4.585252499999999</v>
+        <v>4.5684</v>
       </c>
       <c r="O41">
-        <v>0.7794929249999999</v>
+        <v>0.776628</v>
       </c>
       <c r="P41">
-        <v>3.805759574999999</v>
+        <v>3.791771999999999</v>
       </c>
       <c r="Q41">
-        <v>5.875759574999999</v>
+        <v>5.861771999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1108562198966905</v>
+        <v>0.1118200673586564</v>
       </c>
       <c r="T41">
-        <v>1.50245311539701</v>
+        <v>1.524712872024397</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.976447228783677</v>
+        <v>7.777036048064084</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08485404041519384</v>
+        <v>0.08504007669340646</v>
       </c>
       <c r="C42">
-        <v>18.98449266587367</v>
+        <v>18.61504467040203</v>
       </c>
       <c r="D42">
-        <v>25.24449266587367</v>
+        <v>25.19004467040203</v>
       </c>
       <c r="E42">
-        <v>-7.099999999999998</v>
+        <v>-6.784999999999998</v>
       </c>
       <c r="F42">
-        <v>12.6</v>
+        <v>12.915</v>
       </c>
       <c r="G42">
         <v>6.34</v>
@@ -4725,45 +4725,45 @@
         <v>5.2425</v>
       </c>
       <c r="M42">
-        <v>0.6741</v>
+        <v>0.7012845000000001</v>
       </c>
       <c r="N42">
-        <v>4.5684</v>
+        <v>4.5412155</v>
       </c>
       <c r="O42">
-        <v>0.776628</v>
+        <v>0.772006635</v>
       </c>
       <c r="P42">
-        <v>3.791771999999999</v>
+        <v>3.769208865</v>
       </c>
       <c r="Q42">
-        <v>5.861771999999999</v>
+        <v>5.839208865</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1118200673586564</v>
+        <v>0.1128165876159432</v>
       </c>
       <c r="T42">
-        <v>1.524712872024397</v>
+        <v>1.547727196673053</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.17</v>
       </c>
       <c r="W42">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.777036048064084</v>
+        <v>7.475568046919616</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08504007669340646</v>
+        <v>0.08496051297161909</v>
       </c>
       <c r="C43">
-        <v>18.61504467040203</v>
+        <v>18.32330213797596</v>
       </c>
       <c r="D43">
-        <v>25.19004467040203</v>
+        <v>25.21330213797596</v>
       </c>
       <c r="E43">
-        <v>-6.784999999999998</v>
+        <v>-6.469999999999999</v>
       </c>
       <c r="F43">
-        <v>12.915</v>
+        <v>13.23</v>
       </c>
       <c r="G43">
         <v>6.34</v>
@@ -4807,28 +4807,28 @@
         <v>5.2425</v>
       </c>
       <c r="M43">
-        <v>0.7012845000000001</v>
+        <v>0.7183890000000001</v>
       </c>
       <c r="N43">
-        <v>4.5412155</v>
+        <v>4.524111</v>
       </c>
       <c r="O43">
-        <v>0.772006635</v>
+        <v>0.76909887</v>
       </c>
       <c r="P43">
-        <v>3.769208865</v>
+        <v>3.755012129999999</v>
       </c>
       <c r="Q43">
-        <v>5.839208865</v>
+        <v>5.825012129999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1128165876159432</v>
+        <v>0.1138474706407226</v>
       </c>
       <c r="T43">
-        <v>1.547727196673053</v>
+        <v>1.571535118723386</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.475568046919616</v>
+        <v>7.297578331516767</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08496051297161911</v>
+        <v>0.08488094924983175</v>
       </c>
       <c r="C44">
-        <v>18.32330213797595</v>
+        <v>18.0316025915531</v>
       </c>
       <c r="D44">
-        <v>25.21330213797595</v>
+        <v>25.2366025915531</v>
       </c>
       <c r="E44">
-        <v>-6.470000000000001</v>
+        <v>-6.154999999999999</v>
       </c>
       <c r="F44">
-        <v>13.23</v>
+        <v>13.545</v>
       </c>
       <c r="G44">
         <v>6.34</v>
@@ -4889,28 +4889,28 @@
         <v>5.2425</v>
       </c>
       <c r="M44">
-        <v>0.7183889999999999</v>
+        <v>0.7354935</v>
       </c>
       <c r="N44">
-        <v>4.524111</v>
+        <v>4.507006499999999</v>
       </c>
       <c r="O44">
-        <v>0.76909887</v>
+        <v>0.7661911049999999</v>
       </c>
       <c r="P44">
-        <v>3.755012129999999</v>
+        <v>3.740815394999999</v>
       </c>
       <c r="Q44">
-        <v>5.825012129999999</v>
+        <v>5.810815394999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1138474706407226</v>
+        <v>0.1149145249997048</v>
       </c>
       <c r="T44">
-        <v>1.571535118723385</v>
+        <v>1.596178406459695</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.297578331516768</v>
+        <v>7.127867207528006</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08488094924983175</v>
+        <v>0.08480138552804437</v>
       </c>
       <c r="C45">
-        <v>18.0316025915531</v>
+        <v>17.73994615041812</v>
       </c>
       <c r="D45">
-        <v>25.2366025915531</v>
+        <v>25.25994615041812</v>
       </c>
       <c r="E45">
-        <v>-6.154999999999999</v>
+        <v>-5.84</v>
       </c>
       <c r="F45">
-        <v>13.545</v>
+        <v>13.86</v>
       </c>
       <c r="G45">
         <v>6.34</v>
@@ -4971,28 +4971,28 @@
         <v>5.2425</v>
       </c>
       <c r="M45">
-        <v>0.7354935</v>
+        <v>0.752598</v>
       </c>
       <c r="N45">
-        <v>4.507006499999999</v>
+        <v>4.489902</v>
       </c>
       <c r="O45">
-        <v>0.7661911049999999</v>
+        <v>0.76328334</v>
       </c>
       <c r="P45">
-        <v>3.740815394999999</v>
+        <v>3.72661866</v>
       </c>
       <c r="Q45">
-        <v>5.810815394999999</v>
+        <v>5.79661866</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1149145249997048</v>
+        <v>0.1160196884429364</v>
       </c>
       <c r="T45">
-        <v>1.596178406459695</v>
+        <v>1.621701811615159</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.127867207528006</v>
+        <v>6.965870225538734</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08480138552804437</v>
+        <v>0.08472182180625699</v>
       </c>
       <c r="C46">
-        <v>17.73994615041812</v>
+        <v>17.44833293429739</v>
       </c>
       <c r="D46">
-        <v>25.25994615041812</v>
+        <v>25.28333293429739</v>
       </c>
       <c r="E46">
-        <v>-5.84</v>
+        <v>-5.524999999999999</v>
       </c>
       <c r="F46">
-        <v>13.86</v>
+        <v>14.175</v>
       </c>
       <c r="G46">
         <v>6.34</v>
@@ -5053,28 +5053,28 @@
         <v>5.2425</v>
       </c>
       <c r="M46">
-        <v>0.752598</v>
+        <v>0.7697025000000001</v>
       </c>
       <c r="N46">
-        <v>4.489902</v>
+        <v>4.4727975</v>
       </c>
       <c r="O46">
-        <v>0.76328334</v>
+        <v>0.760375575</v>
       </c>
       <c r="P46">
-        <v>3.72661866</v>
+        <v>3.712421925</v>
       </c>
       <c r="Q46">
-        <v>5.79661866</v>
+        <v>5.782421925</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1160196884429364</v>
+        <v>0.11716503964774</v>
       </c>
       <c r="T46">
-        <v>1.621701811615159</v>
+        <v>1.648153340594457</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.965870225538734</v>
+        <v>6.811073109415649</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08472182180625699</v>
+        <v>0.08464225808446964</v>
       </c>
       <c r="C47">
-        <v>17.44833293429739</v>
+        <v>17.15676306336108</v>
       </c>
       <c r="D47">
-        <v>25.28333293429739</v>
+        <v>25.30676306336109</v>
       </c>
       <c r="E47">
-        <v>-5.524999999999999</v>
+        <v>-5.209999999999999</v>
       </c>
       <c r="F47">
-        <v>14.175</v>
+        <v>14.49</v>
       </c>
       <c r="G47">
         <v>6.34</v>
@@ -5135,28 +5135,28 @@
         <v>5.2425</v>
       </c>
       <c r="M47">
-        <v>0.7697025000000001</v>
+        <v>0.786807</v>
       </c>
       <c r="N47">
-        <v>4.4727975</v>
+        <v>4.455693</v>
       </c>
       <c r="O47">
-        <v>0.760375575</v>
+        <v>0.7574678100000001</v>
       </c>
       <c r="P47">
-        <v>3.712421925</v>
+        <v>3.69822519</v>
       </c>
       <c r="Q47">
-        <v>5.782421925</v>
+        <v>5.76822519</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.11716503964774</v>
+        <v>0.1183528112675364</v>
       </c>
       <c r="T47">
-        <v>1.648153340594457</v>
+        <v>1.675584555832248</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.811073109415649</v>
+        <v>6.663006302689223</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08464225808446964</v>
+        <v>0.08456269436268225</v>
       </c>
       <c r="C48">
-        <v>17.15676306336108</v>
+        <v>16.86523665822529</v>
       </c>
       <c r="D48">
-        <v>25.30676306336109</v>
+        <v>25.33023665822529</v>
       </c>
       <c r="E48">
-        <v>-5.209999999999999</v>
+        <v>-4.894999999999998</v>
       </c>
       <c r="F48">
-        <v>14.49</v>
+        <v>14.805</v>
       </c>
       <c r="G48">
         <v>6.34</v>
@@ -5217,28 +5217,28 @@
         <v>5.2425</v>
       </c>
       <c r="M48">
-        <v>0.786807</v>
+        <v>0.8039115000000001</v>
       </c>
       <c r="N48">
-        <v>4.455693</v>
+        <v>4.4385885</v>
       </c>
       <c r="O48">
-        <v>0.7574678100000001</v>
+        <v>0.7545600450000001</v>
       </c>
       <c r="P48">
-        <v>3.69822519</v>
+        <v>3.684028455</v>
       </c>
       <c r="Q48">
-        <v>5.76822519</v>
+        <v>5.754028455</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1183528112675364</v>
+        <v>0.119585404457891</v>
       </c>
       <c r="T48">
-        <v>1.675584555832248</v>
+        <v>1.704050911267692</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.663006302689223</v>
+        <v>6.521240211142644</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08456269436268225</v>
+        <v>0.0844831306408949</v>
       </c>
       <c r="C49">
-        <v>16.86523665822529</v>
+        <v>16.57375383995397</v>
       </c>
       <c r="D49">
-        <v>25.33023665822529</v>
+        <v>25.35375383995397</v>
       </c>
       <c r="E49">
-        <v>-4.894999999999998</v>
+        <v>-4.579999999999998</v>
       </c>
       <c r="F49">
-        <v>14.805</v>
+        <v>15.12</v>
       </c>
       <c r="G49">
         <v>6.34</v>
@@ -5299,28 +5299,28 @@
         <v>5.2425</v>
       </c>
       <c r="M49">
-        <v>0.8039115000000001</v>
+        <v>0.8210160000000001</v>
       </c>
       <c r="N49">
-        <v>4.4385885</v>
+        <v>4.421484</v>
       </c>
       <c r="O49">
-        <v>0.7545600450000001</v>
+        <v>0.75165228</v>
       </c>
       <c r="P49">
-        <v>3.684028455</v>
+        <v>3.669831719999999</v>
       </c>
       <c r="Q49">
-        <v>5.754028455</v>
+        <v>5.73983172</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.119585404457891</v>
+        <v>0.120865405078644</v>
       </c>
       <c r="T49">
-        <v>1.704050911267692</v>
+        <v>1.733612126527575</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.521240211142644</v>
+        <v>6.385381040077172</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08448313064089488</v>
+        <v>0.08440356691910751</v>
       </c>
       <c r="C50">
-        <v>16.57375383995397</v>
+        <v>16.28231473006114</v>
       </c>
       <c r="D50">
-        <v>25.35375383995397</v>
+        <v>25.37731473006114</v>
       </c>
       <c r="E50">
-        <v>-4.58</v>
+        <v>-4.264999999999999</v>
       </c>
       <c r="F50">
-        <v>15.12</v>
+        <v>15.435</v>
       </c>
       <c r="G50">
         <v>6.34</v>
@@ -5381,28 +5381,28 @@
         <v>5.2425</v>
       </c>
       <c r="M50">
-        <v>0.821016</v>
+        <v>0.8381205</v>
       </c>
       <c r="N50">
-        <v>4.421484</v>
+        <v>4.404379499999999</v>
       </c>
       <c r="O50">
-        <v>0.75165228</v>
+        <v>0.7487445149999999</v>
       </c>
       <c r="P50">
-        <v>3.669831719999999</v>
+        <v>3.655634984999999</v>
       </c>
       <c r="Q50">
-        <v>5.73983172</v>
+        <v>5.725634984999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.120865405078644</v>
+        <v>0.1221956018021716</v>
       </c>
       <c r="T50">
-        <v>1.733612126527575</v>
+        <v>1.764332605130984</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.385381040077172</v>
+        <v>6.255067141300087</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08440356691910751</v>
+        <v>0.08432400319732014</v>
       </c>
       <c r="C51">
-        <v>16.28231473006114</v>
+        <v>15.99091945051288</v>
       </c>
       <c r="D51">
-        <v>25.37731473006114</v>
+        <v>25.40091945051288</v>
       </c>
       <c r="E51">
-        <v>-4.264999999999999</v>
+        <v>-3.949999999999999</v>
       </c>
       <c r="F51">
-        <v>15.435</v>
+        <v>15.75</v>
       </c>
       <c r="G51">
         <v>6.34</v>
@@ -5463,28 +5463,28 @@
         <v>5.2425</v>
       </c>
       <c r="M51">
-        <v>0.8381205</v>
+        <v>0.855225</v>
       </c>
       <c r="N51">
-        <v>4.404379499999999</v>
+        <v>4.387275</v>
       </c>
       <c r="O51">
-        <v>0.7487445149999999</v>
+        <v>0.74583675</v>
       </c>
       <c r="P51">
-        <v>3.655634984999999</v>
+        <v>3.64143825</v>
       </c>
       <c r="Q51">
-        <v>5.725634984999999</v>
+        <v>5.71143825</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1221956018021716</v>
+        <v>0.1235790063946403</v>
       </c>
       <c r="T51">
-        <v>1.764332605130984</v>
+        <v>1.796281902878529</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.255067141300087</v>
+        <v>6.129965798474085</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08432400319732014</v>
+        <v>0.08466773947553276</v>
       </c>
       <c r="C52">
-        <v>15.99091945051288</v>
+        <v>15.57425451254413</v>
       </c>
       <c r="D52">
-        <v>25.40091945051288</v>
+        <v>25.29925451254413</v>
       </c>
       <c r="E52">
-        <v>-3.949999999999999</v>
+        <v>-3.634999999999998</v>
       </c>
       <c r="F52">
-        <v>15.75</v>
+        <v>16.065</v>
       </c>
       <c r="G52">
         <v>6.34</v>
@@ -5545,45 +5545,45 @@
         <v>5.2425</v>
       </c>
       <c r="M52">
-        <v>0.855225</v>
+        <v>0.8883945000000001</v>
       </c>
       <c r="N52">
-        <v>4.387275</v>
+        <v>4.354105499999999</v>
       </c>
       <c r="O52">
-        <v>0.74583675</v>
+        <v>0.740197935</v>
       </c>
       <c r="P52">
-        <v>3.64143825</v>
+        <v>3.613907564999999</v>
       </c>
       <c r="Q52">
-        <v>5.71143825</v>
+        <v>5.683907564999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1235790063946403</v>
+        <v>0.1250188764806791</v>
       </c>
       <c r="T52">
-        <v>1.796281902878529</v>
+        <v>1.829535253595361</v>
       </c>
       <c r="U52">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.17</v>
       </c>
       <c r="W52">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>6.129965798474085</v>
+        <v>5.901094615061213</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08466773947553276</v>
+        <v>0.0845964757537454</v>
       </c>
       <c r="C53">
-        <v>15.57425451254413</v>
+        <v>15.28026485525198</v>
       </c>
       <c r="D53">
-        <v>25.29925451254413</v>
+        <v>25.32026485525198</v>
       </c>
       <c r="E53">
-        <v>-3.634999999999998</v>
+        <v>-3.32</v>
       </c>
       <c r="F53">
-        <v>16.065</v>
+        <v>16.38</v>
       </c>
       <c r="G53">
         <v>6.34</v>
@@ -5627,28 +5627,28 @@
         <v>5.2425</v>
       </c>
       <c r="M53">
-        <v>0.8883945000000001</v>
+        <v>0.905814</v>
       </c>
       <c r="N53">
-        <v>4.354105499999999</v>
+        <v>4.336685999999999</v>
       </c>
       <c r="O53">
-        <v>0.740197935</v>
+        <v>0.7372366199999999</v>
       </c>
       <c r="P53">
-        <v>3.613907564999999</v>
+        <v>3.599449379999999</v>
       </c>
       <c r="Q53">
-        <v>5.683907564999999</v>
+        <v>5.66944938</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1250188764806791</v>
+        <v>0.1265187411536363</v>
       </c>
       <c r="T53">
-        <v>1.829535253595361</v>
+        <v>1.864174160592061</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.901094615061213</v>
+        <v>5.787612026310036</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0845964757537454</v>
+        <v>0.08452521203195804</v>
       </c>
       <c r="C54">
-        <v>15.28026485525198</v>
+        <v>14.9863101240012</v>
       </c>
       <c r="D54">
-        <v>25.32026485525198</v>
+        <v>25.3413101240012</v>
       </c>
       <c r="E54">
-        <v>-3.32</v>
+        <v>-3.004999999999999</v>
       </c>
       <c r="F54">
-        <v>16.38</v>
+        <v>16.695</v>
       </c>
       <c r="G54">
         <v>6.34</v>
@@ -5709,28 +5709,28 @@
         <v>5.2425</v>
       </c>
       <c r="M54">
-        <v>0.905814</v>
+        <v>0.9232335</v>
       </c>
       <c r="N54">
-        <v>4.336685999999999</v>
+        <v>4.319266499999999</v>
       </c>
       <c r="O54">
-        <v>0.7372366199999999</v>
+        <v>0.7342753049999999</v>
       </c>
       <c r="P54">
-        <v>3.599449379999999</v>
+        <v>3.584991195</v>
       </c>
       <c r="Q54">
-        <v>5.66944938</v>
+        <v>5.654991194999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1265187411536363</v>
+        <v>0.1280824298552299</v>
       </c>
       <c r="T54">
-        <v>1.864174160592061</v>
+        <v>1.900287063631175</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.787612026310036</v>
+        <v>5.678411799398527</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08452521203195804</v>
+        <v>0.08445394831017065</v>
       </c>
       <c r="C55">
-        <v>14.9863101240012</v>
+        <v>14.69239040595193</v>
       </c>
       <c r="D55">
-        <v>25.3413101240012</v>
+        <v>25.36239040595193</v>
       </c>
       <c r="E55">
-        <v>-3.004999999999999</v>
+        <v>-2.689999999999998</v>
       </c>
       <c r="F55">
-        <v>16.695</v>
+        <v>17.01</v>
       </c>
       <c r="G55">
         <v>6.34</v>
@@ -5791,28 +5791,28 @@
         <v>5.2425</v>
       </c>
       <c r="M55">
-        <v>0.9232335</v>
+        <v>0.9406530000000001</v>
       </c>
       <c r="N55">
-        <v>4.319266499999999</v>
+        <v>4.301847</v>
       </c>
       <c r="O55">
-        <v>0.7342753049999999</v>
+        <v>0.73131399</v>
       </c>
       <c r="P55">
-        <v>3.584991195</v>
+        <v>3.57053301</v>
       </c>
       <c r="Q55">
-        <v>5.654991194999999</v>
+        <v>5.64053301</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1280824298552299</v>
+        <v>0.1297141050221101</v>
       </c>
       <c r="T55">
-        <v>1.900287063631175</v>
+        <v>1.937970092889379</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.678411799398527</v>
+        <v>5.57325602533559</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08445394831017065</v>
+        <v>0.08438268458838329</v>
       </c>
       <c r="C56">
-        <v>14.69239040595193</v>
+        <v>14.39850578855458</v>
       </c>
       <c r="D56">
-        <v>25.36239040595193</v>
+        <v>25.38350578855458</v>
       </c>
       <c r="E56">
-        <v>-2.689999999999998</v>
+        <v>-2.374999999999996</v>
       </c>
       <c r="F56">
-        <v>17.01</v>
+        <v>17.325</v>
       </c>
       <c r="G56">
         <v>6.34</v>
@@ -5873,28 +5873,28 @@
         <v>5.2425</v>
       </c>
       <c r="M56">
-        <v>0.9406530000000001</v>
+        <v>0.9580725000000002</v>
       </c>
       <c r="N56">
-        <v>4.301847</v>
+        <v>4.2844275</v>
       </c>
       <c r="O56">
-        <v>0.73131399</v>
+        <v>0.728352675</v>
       </c>
       <c r="P56">
-        <v>3.57053301</v>
+        <v>3.556074825</v>
       </c>
       <c r="Q56">
-        <v>5.64053301</v>
+        <v>5.626074825</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1297141050221101</v>
+        <v>0.1314182990852962</v>
       </c>
       <c r="T56">
-        <v>1.937970092889379</v>
+        <v>1.977327923447949</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.57325602533559</v>
+        <v>5.471924097602216</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08438268458838329</v>
+        <v>0.08431142086659592</v>
       </c>
       <c r="C57">
-        <v>14.39850578855458</v>
+        <v>14.10465635955103</v>
       </c>
       <c r="D57">
-        <v>25.38350578855458</v>
+        <v>25.40465635955103</v>
       </c>
       <c r="E57">
-        <v>-2.374999999999996</v>
+        <v>-2.059999999999999</v>
       </c>
       <c r="F57">
-        <v>17.325</v>
+        <v>17.64</v>
       </c>
       <c r="G57">
         <v>6.34</v>
@@ -5955,28 +5955,28 @@
         <v>5.2425</v>
       </c>
       <c r="M57">
-        <v>0.9580725000000002</v>
+        <v>0.975492</v>
       </c>
       <c r="N57">
-        <v>4.2844275</v>
+        <v>4.267008</v>
       </c>
       <c r="O57">
-        <v>0.728352675</v>
+        <v>0.72539136</v>
       </c>
       <c r="P57">
-        <v>3.556074825</v>
+        <v>3.54161664</v>
       </c>
       <c r="Q57">
-        <v>5.626074825</v>
+        <v>5.611616639999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1314182990852962</v>
+        <v>0.1331999565149907</v>
       </c>
       <c r="T57">
-        <v>1.977327923447949</v>
+        <v>2.018474746304636</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.471924097602216</v>
+        <v>5.374211167287891</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08431142086659592</v>
+        <v>0.08424015714480855</v>
       </c>
       <c r="C58">
-        <v>14.10465635955103</v>
+        <v>13.81084220697584</v>
       </c>
       <c r="D58">
-        <v>25.40465635955103</v>
+        <v>25.42584220697584</v>
       </c>
       <c r="E58">
-        <v>-2.059999999999999</v>
+        <v>-1.744999999999997</v>
       </c>
       <c r="F58">
-        <v>17.64</v>
+        <v>17.955</v>
       </c>
       <c r="G58">
         <v>6.34</v>
@@ -6037,28 +6037,28 @@
         <v>5.2425</v>
       </c>
       <c r="M58">
-        <v>0.975492</v>
+        <v>0.9929115000000002</v>
       </c>
       <c r="N58">
-        <v>4.267008</v>
+        <v>4.2495885</v>
       </c>
       <c r="O58">
-        <v>0.72539136</v>
+        <v>0.722430045</v>
       </c>
       <c r="P58">
-        <v>3.54161664</v>
+        <v>3.527158455</v>
       </c>
       <c r="Q58">
-        <v>5.611616639999999</v>
+        <v>5.597158455</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1331999565149907</v>
+        <v>0.1350644817321129</v>
       </c>
       <c r="T58">
-        <v>2.018474746304636</v>
+        <v>2.061535374875587</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.374211167287891</v>
+        <v>5.279926760844243</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08424015714480855</v>
+        <v>0.08416889342302117</v>
       </c>
       <c r="C59">
-        <v>13.81084220697584</v>
+        <v>13.51706341915749</v>
       </c>
       <c r="D59">
-        <v>25.42584220697584</v>
+        <v>25.44706341915749</v>
       </c>
       <c r="E59">
-        <v>-1.744999999999997</v>
+        <v>-1.429999999999996</v>
       </c>
       <c r="F59">
-        <v>17.955</v>
+        <v>18.27</v>
       </c>
       <c r="G59">
         <v>6.34</v>
@@ -6119,28 +6119,28 @@
         <v>5.2425</v>
       </c>
       <c r="M59">
-        <v>0.9929115000000002</v>
+        <v>1.010331</v>
       </c>
       <c r="N59">
-        <v>4.2495885</v>
+        <v>4.232168999999999</v>
       </c>
       <c r="O59">
-        <v>0.722430045</v>
+        <v>0.7194687299999999</v>
       </c>
       <c r="P59">
-        <v>3.527158455</v>
+        <v>3.512700269999999</v>
       </c>
       <c r="Q59">
-        <v>5.597158455</v>
+        <v>5.582700269999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1350644817321129</v>
+        <v>0.1370177938643361</v>
       </c>
       <c r="T59">
-        <v>2.061535374875587</v>
+        <v>2.106646509568964</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.279926760844243</v>
+        <v>5.188893540829686</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08416889342302118</v>
+        <v>0.0840976297012338</v>
       </c>
       <c r="C60">
-        <v>13.51706341915748</v>
+        <v>13.22332008471957</v>
       </c>
       <c r="D60">
-        <v>25.44706341915748</v>
+        <v>25.46832008471957</v>
       </c>
       <c r="E60">
-        <v>-1.43</v>
+        <v>-1.115000000000002</v>
       </c>
       <c r="F60">
-        <v>18.27</v>
+        <v>18.585</v>
       </c>
       <c r="G60">
         <v>6.34</v>
@@ -6201,28 +6201,28 @@
         <v>5.2425</v>
       </c>
       <c r="M60">
-        <v>1.010331</v>
+        <v>1.0277505</v>
       </c>
       <c r="N60">
-        <v>4.232169</v>
+        <v>4.2147495</v>
       </c>
       <c r="O60">
-        <v>0.71946873</v>
+        <v>0.716507415</v>
       </c>
       <c r="P60">
-        <v>3.51270027</v>
+        <v>3.498242085</v>
       </c>
       <c r="Q60">
-        <v>5.58270027</v>
+        <v>5.568242085</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1370177938643361</v>
+        <v>0.1390663895152044</v>
       </c>
       <c r="T60">
-        <v>2.106646509568964</v>
+        <v>2.153958187418116</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.188893540829688</v>
+        <v>5.100946192680033</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0840976297012338</v>
+        <v>0.08402636597944645</v>
       </c>
       <c r="C61">
-        <v>13.22332008471957</v>
+        <v>12.92961229258205</v>
       </c>
       <c r="D61">
-        <v>25.46832008471957</v>
+        <v>25.48961229258204</v>
       </c>
       <c r="E61">
-        <v>-1.115000000000002</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="F61">
-        <v>18.585</v>
+        <v>18.9</v>
       </c>
       <c r="G61">
         <v>6.34</v>
@@ -6283,28 +6283,28 @@
         <v>5.2425</v>
       </c>
       <c r="M61">
-        <v>1.0277505</v>
+        <v>1.04517</v>
       </c>
       <c r="N61">
-        <v>4.2147495</v>
+        <v>4.19733</v>
       </c>
       <c r="O61">
-        <v>0.716507415</v>
+        <v>0.7135461000000001</v>
       </c>
       <c r="P61">
-        <v>3.498242085</v>
+        <v>3.4837839</v>
       </c>
       <c r="Q61">
-        <v>5.568242085</v>
+        <v>5.553783899999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1390663895152044</v>
+        <v>0.1412174149486161</v>
       </c>
       <c r="T61">
-        <v>2.153958187418116</v>
+        <v>2.203635449159725</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.100946192680033</v>
+        <v>5.015930422802032</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08402636597944645</v>
+        <v>0.08395510225765906</v>
       </c>
       <c r="C62">
-        <v>12.92961229258205</v>
+        <v>12.63594013196251</v>
       </c>
       <c r="D62">
-        <v>25.48961229258204</v>
+        <v>25.51094013196251</v>
       </c>
       <c r="E62">
-        <v>-0.8000000000000007</v>
+        <v>-0.4849999999999994</v>
       </c>
       <c r="F62">
-        <v>18.9</v>
+        <v>19.215</v>
       </c>
       <c r="G62">
         <v>6.34</v>
@@ -6365,28 +6365,28 @@
         <v>5.2425</v>
       </c>
       <c r="M62">
-        <v>1.04517</v>
+        <v>1.0625895</v>
       </c>
       <c r="N62">
-        <v>4.19733</v>
+        <v>4.1799105</v>
       </c>
       <c r="O62">
-        <v>0.7135461000000001</v>
+        <v>0.7105847850000001</v>
       </c>
       <c r="P62">
-        <v>3.4837839</v>
+        <v>3.469325715</v>
       </c>
       <c r="Q62">
-        <v>5.553783899999999</v>
+        <v>5.539325715</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1412174149486161</v>
+        <v>0.143478749378613</v>
       </c>
       <c r="T62">
-        <v>2.203635449159725</v>
+        <v>2.255860262785519</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.015930422802032</v>
+        <v>4.933702055215114</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08395510225765906</v>
+        <v>0.08388383853587168</v>
       </c>
       <c r="C63">
-        <v>12.63594013196251</v>
+        <v>12.34230369237739</v>
       </c>
       <c r="D63">
-        <v>25.51094013196251</v>
+        <v>25.53230369237739</v>
       </c>
       <c r="E63">
-        <v>-0.4849999999999994</v>
+        <v>-0.1699999999999982</v>
       </c>
       <c r="F63">
-        <v>19.215</v>
+        <v>19.53</v>
       </c>
       <c r="G63">
         <v>6.34</v>
@@ -6447,28 +6447,28 @@
         <v>5.2425</v>
       </c>
       <c r="M63">
-        <v>1.0625895</v>
+        <v>1.080009</v>
       </c>
       <c r="N63">
-        <v>4.1799105</v>
+        <v>4.162490999999999</v>
       </c>
       <c r="O63">
-        <v>0.7105847850000001</v>
+        <v>0.7076234699999999</v>
       </c>
       <c r="P63">
-        <v>3.469325715</v>
+        <v>3.45486753</v>
       </c>
       <c r="Q63">
-        <v>5.539325715</v>
+        <v>5.52486753</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.143478749378613</v>
+        <v>0.1458591014101887</v>
       </c>
       <c r="T63">
-        <v>2.255860262785519</v>
+        <v>2.310833750812671</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.933702055215114</v>
+        <v>4.854126215614869</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08388383853587168</v>
+        <v>0.08381257481408431</v>
       </c>
       <c r="C64">
-        <v>12.34230369237739</v>
+        <v>12.0487030636432</v>
       </c>
       <c r="D64">
-        <v>25.53230369237739</v>
+        <v>25.5537030636432</v>
       </c>
       <c r="E64">
-        <v>-0.1699999999999982</v>
+        <v>0.1449999999999996</v>
       </c>
       <c r="F64">
-        <v>19.53</v>
+        <v>19.845</v>
       </c>
       <c r="G64">
         <v>6.34</v>
@@ -6529,28 +6529,28 @@
         <v>5.2425</v>
       </c>
       <c r="M64">
-        <v>1.080009</v>
+        <v>1.0974285</v>
       </c>
       <c r="N64">
-        <v>4.162490999999999</v>
+        <v>4.1450715</v>
       </c>
       <c r="O64">
-        <v>0.7076234699999999</v>
+        <v>0.7046621550000001</v>
       </c>
       <c r="P64">
-        <v>3.45486753</v>
+        <v>3.440409345</v>
       </c>
       <c r="Q64">
-        <v>5.52486753</v>
+        <v>5.510409344999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1458591014101887</v>
+        <v>0.1483681211191468</v>
       </c>
       <c r="T64">
-        <v>2.310833750812671</v>
+        <v>2.368778778733183</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.854126215614869</v>
+        <v>4.777076593144793</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08381257481408431</v>
+        <v>0.08374131109229696</v>
       </c>
       <c r="C65">
-        <v>12.0487030636432</v>
+        <v>11.75513833587785</v>
       </c>
       <c r="D65">
-        <v>25.5537030636432</v>
+        <v>25.57513833587785</v>
       </c>
       <c r="E65">
-        <v>0.1449999999999996</v>
+        <v>0.4600000000000009</v>
       </c>
       <c r="F65">
-        <v>19.845</v>
+        <v>20.16</v>
       </c>
       <c r="G65">
         <v>6.34</v>
@@ -6611,28 +6611,28 @@
         <v>5.2425</v>
       </c>
       <c r="M65">
-        <v>1.0974285</v>
+        <v>1.114848</v>
       </c>
       <c r="N65">
-        <v>4.1450715</v>
+        <v>4.127651999999999</v>
       </c>
       <c r="O65">
-        <v>0.7046621550000001</v>
+        <v>0.70170084</v>
       </c>
       <c r="P65">
-        <v>3.440409345</v>
+        <v>3.425951159999999</v>
       </c>
       <c r="Q65">
-        <v>5.510409344999999</v>
+        <v>5.495951159999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1483681211191468</v>
+        <v>0.151016530811936</v>
       </c>
       <c r="T65">
-        <v>2.368778778733183</v>
+        <v>2.4299429748715</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.777076593144793</v>
+        <v>4.702434771376904</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08374131109229696</v>
+        <v>0.08367004737050959</v>
       </c>
       <c r="C66">
-        <v>11.75513833587785</v>
+        <v>11.46160959950187</v>
       </c>
       <c r="D66">
-        <v>25.57513833587785</v>
+        <v>25.59660959950187</v>
       </c>
       <c r="E66">
-        <v>0.4600000000000009</v>
+        <v>0.7750000000000021</v>
       </c>
       <c r="F66">
-        <v>20.16</v>
+        <v>20.475</v>
       </c>
       <c r="G66">
         <v>6.34</v>
@@ -6693,28 +6693,28 @@
         <v>5.2425</v>
       </c>
       <c r="M66">
-        <v>1.114848</v>
+        <v>1.1322675</v>
       </c>
       <c r="N66">
-        <v>4.127651999999999</v>
+        <v>4.1102325</v>
       </c>
       <c r="O66">
-        <v>0.70170084</v>
+        <v>0.6987395249999999</v>
       </c>
       <c r="P66">
-        <v>3.425951159999999</v>
+        <v>3.411492975</v>
       </c>
       <c r="Q66">
-        <v>5.495951159999999</v>
+        <v>5.481492975</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.151016530811936</v>
+        <v>0.153816278201456</v>
       </c>
       <c r="T66">
-        <v>2.4299429748715</v>
+        <v>2.494602267932009</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.702434771376904</v>
+        <v>4.630089621048029</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08367004737050959</v>
+        <v>0.08359878364872221</v>
       </c>
       <c r="C67">
-        <v>11.46160959950187</v>
+        <v>11.16811694523969</v>
       </c>
       <c r="D67">
-        <v>25.59660959950187</v>
+        <v>25.6181169452397</v>
       </c>
       <c r="E67">
-        <v>0.7750000000000021</v>
+        <v>1.090000000000003</v>
       </c>
       <c r="F67">
-        <v>20.475</v>
+        <v>20.79</v>
       </c>
       <c r="G67">
         <v>6.34</v>
@@ -6775,28 +6775,28 @@
         <v>5.2425</v>
       </c>
       <c r="M67">
-        <v>1.1322675</v>
+        <v>1.149687</v>
       </c>
       <c r="N67">
-        <v>4.1102325</v>
+        <v>4.092813</v>
       </c>
       <c r="O67">
-        <v>0.6987395249999999</v>
+        <v>0.69577821</v>
       </c>
       <c r="P67">
-        <v>3.411492975</v>
+        <v>3.39703479</v>
       </c>
       <c r="Q67">
-        <v>5.481492975</v>
+        <v>5.46703479</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.153816278201456</v>
+        <v>0.1567807166138889</v>
       </c>
       <c r="T67">
-        <v>2.494602267932009</v>
+        <v>2.563065048819604</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.630089621048029</v>
+        <v>4.559936748001847</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08359878364872221</v>
+        <v>0.08491776992693484</v>
       </c>
       <c r="C68">
-        <v>11.16811694523969</v>
+        <v>10.46081420447133</v>
       </c>
       <c r="D68">
-        <v>25.6181169452397</v>
+        <v>25.22581420447133</v>
       </c>
       <c r="E68">
-        <v>1.090000000000003</v>
+        <v>1.405000000000001</v>
       </c>
       <c r="F68">
-        <v>20.79</v>
+        <v>21.105</v>
       </c>
       <c r="G68">
         <v>6.34</v>
@@ -6857,45 +6857,45 @@
         <v>5.2425</v>
       </c>
       <c r="M68">
-        <v>1.149687</v>
+        <v>1.219869</v>
       </c>
       <c r="N68">
-        <v>4.092813</v>
+        <v>4.022631</v>
       </c>
       <c r="O68">
-        <v>0.69577821</v>
+        <v>0.68384727</v>
       </c>
       <c r="P68">
-        <v>3.39703479</v>
+        <v>3.338783729999999</v>
       </c>
       <c r="Q68">
-        <v>5.46703479</v>
+        <v>5.40878373</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1567807166138889</v>
+        <v>0.1599248179604086</v>
       </c>
       <c r="T68">
-        <v>2.563065048819604</v>
+        <v>2.635677089154933</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.17</v>
       </c>
       <c r="W68">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.559936748001847</v>
+        <v>4.297592610354062</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08491776992693484</v>
+        <v>0.08486725620514746</v>
       </c>
       <c r="C69">
-        <v>10.46081420447133</v>
+        <v>10.16061698143201</v>
       </c>
       <c r="D69">
-        <v>25.22581420447133</v>
+        <v>25.24061698143201</v>
       </c>
       <c r="E69">
-        <v>1.405000000000001</v>
+        <v>1.720000000000002</v>
       </c>
       <c r="F69">
-        <v>21.105</v>
+        <v>21.42</v>
       </c>
       <c r="G69">
         <v>6.34</v>
@@ -6939,28 +6939,28 @@
         <v>5.2425</v>
       </c>
       <c r="M69">
-        <v>1.219869</v>
+        <v>1.238076</v>
       </c>
       <c r="N69">
-        <v>4.022631</v>
+        <v>4.004423999999999</v>
       </c>
       <c r="O69">
-        <v>0.68384727</v>
+        <v>0.68075208</v>
       </c>
       <c r="P69">
-        <v>3.338783729999999</v>
+        <v>3.323671919999999</v>
       </c>
       <c r="Q69">
-        <v>5.40878373</v>
+        <v>5.393671919999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1599248179604086</v>
+        <v>0.1632654256410858</v>
       </c>
       <c r="T69">
-        <v>2.635677089154933</v>
+        <v>2.712827382011221</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.297592610354062</v>
+        <v>4.234392719025325</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08486725620514746</v>
+        <v>0.0848167424833601</v>
       </c>
       <c r="C70">
-        <v>10.16061698143201</v>
+        <v>9.860437141448202</v>
       </c>
       <c r="D70">
-        <v>25.24061698143201</v>
+        <v>25.2554371414482</v>
       </c>
       <c r="E70">
-        <v>1.720000000000002</v>
+        <v>2.035000000000004</v>
       </c>
       <c r="F70">
-        <v>21.42</v>
+        <v>21.735</v>
       </c>
       <c r="G70">
         <v>6.34</v>
@@ -7021,28 +7021,28 @@
         <v>5.2425</v>
       </c>
       <c r="M70">
-        <v>1.238076</v>
+        <v>1.256283</v>
       </c>
       <c r="N70">
-        <v>4.004423999999999</v>
+        <v>3.986216999999999</v>
       </c>
       <c r="O70">
-        <v>0.68075208</v>
+        <v>0.67765689</v>
       </c>
       <c r="P70">
-        <v>3.323671919999999</v>
+        <v>3.308560109999999</v>
       </c>
       <c r="Q70">
-        <v>5.393671919999999</v>
+        <v>5.378560109999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1632654256410858</v>
+        <v>0.1668215563979358</v>
       </c>
       <c r="T70">
-        <v>2.712827382011221</v>
+        <v>2.794955113116301</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.234392719025325</v>
+        <v>4.173024708604668</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0848167424833601</v>
+        <v>0.08476622876157272</v>
       </c>
       <c r="C71">
-        <v>9.860437141448202</v>
+        <v>9.560274715157576</v>
       </c>
       <c r="D71">
-        <v>25.2554371414482</v>
+        <v>25.27027471515758</v>
       </c>
       <c r="E71">
-        <v>2.035000000000004</v>
+        <v>2.350000000000001</v>
       </c>
       <c r="F71">
-        <v>21.735</v>
+        <v>22.05</v>
       </c>
       <c r="G71">
         <v>6.34</v>
@@ -7103,28 +7103,28 @@
         <v>5.2425</v>
       </c>
       <c r="M71">
-        <v>1.256283</v>
+        <v>1.27449</v>
       </c>
       <c r="N71">
-        <v>3.986216999999999</v>
+        <v>3.96801</v>
       </c>
       <c r="O71">
-        <v>0.67765689</v>
+        <v>0.6745616999999999</v>
       </c>
       <c r="P71">
-        <v>3.308560109999999</v>
+        <v>3.2934483</v>
       </c>
       <c r="Q71">
-        <v>5.378560109999999</v>
+        <v>5.3634483</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1668215563979358</v>
+        <v>0.1706147625385758</v>
       </c>
       <c r="T71">
-        <v>2.794955113116301</v>
+        <v>2.882558026295052</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.173024708604668</v>
+        <v>4.113410069910317</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08476622876157272</v>
+        <v>0.08471571503978537</v>
       </c>
       <c r="C72">
-        <v>9.560274715157576</v>
+        <v>9.2601297332698</v>
       </c>
       <c r="D72">
-        <v>25.27027471515758</v>
+        <v>25.2851297332698</v>
       </c>
       <c r="E72">
-        <v>2.350000000000001</v>
+        <v>2.665000000000003</v>
       </c>
       <c r="F72">
-        <v>22.05</v>
+        <v>22.365</v>
       </c>
       <c r="G72">
         <v>6.34</v>
@@ -7185,28 +7185,28 @@
         <v>5.2425</v>
       </c>
       <c r="M72">
-        <v>1.27449</v>
+        <v>1.292697</v>
       </c>
       <c r="N72">
-        <v>3.96801</v>
+        <v>3.949802999999999</v>
       </c>
       <c r="O72">
-        <v>0.6745616999999999</v>
+        <v>0.6714665099999999</v>
       </c>
       <c r="P72">
-        <v>3.2934483</v>
+        <v>3.278336489999999</v>
       </c>
       <c r="Q72">
-        <v>5.3634483</v>
+        <v>5.348336489999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1706147625385758</v>
+        <v>0.1746695691027082</v>
       </c>
       <c r="T72">
-        <v>2.882558026295052</v>
+        <v>2.976202519693029</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.113410069910317</v>
+        <v>4.055474716812988</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08471571503978537</v>
+        <v>0.08675680131799798</v>
       </c>
       <c r="C73">
-        <v>9.260129733269803</v>
+        <v>8.358471335466351</v>
       </c>
       <c r="D73">
-        <v>25.2851297332698</v>
+        <v>24.69847133546635</v>
       </c>
       <c r="E73">
-        <v>2.664999999999999</v>
+        <v>2.98</v>
       </c>
       <c r="F73">
-        <v>22.365</v>
+        <v>22.68</v>
       </c>
       <c r="G73">
         <v>6.34</v>
@@ -7267,45 +7267,45 @@
         <v>5.2425</v>
       </c>
       <c r="M73">
-        <v>1.292697</v>
+        <v>1.390284</v>
       </c>
       <c r="N73">
-        <v>3.949803</v>
+        <v>3.852215999999999</v>
       </c>
       <c r="O73">
-        <v>0.67146651</v>
+        <v>0.65487672</v>
       </c>
       <c r="P73">
-        <v>3.27833649</v>
+        <v>3.19733928</v>
       </c>
       <c r="Q73">
-        <v>5.348336489999999</v>
+        <v>5.26733928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1746695691027081</v>
+        <v>0.1790140047071357</v>
       </c>
       <c r="T73">
-        <v>2.976202519693028</v>
+        <v>3.076535905476574</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.17</v>
       </c>
       <c r="W73">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.055474716812988</v>
+        <v>3.770812294466454</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08675680131799798</v>
+        <v>0.0867353375962106</v>
       </c>
       <c r="C74">
-        <v>8.358471335466351</v>
+        <v>8.049498871586596</v>
       </c>
       <c r="D74">
-        <v>24.69847133546635</v>
+        <v>24.7044988715866</v>
       </c>
       <c r="E74">
-        <v>2.98</v>
+        <v>3.295000000000002</v>
       </c>
       <c r="F74">
-        <v>22.68</v>
+        <v>22.995</v>
       </c>
       <c r="G74">
         <v>6.34</v>
@@ -7349,28 +7349,28 @@
         <v>5.2425</v>
       </c>
       <c r="M74">
-        <v>1.390284</v>
+        <v>1.4095935</v>
       </c>
       <c r="N74">
-        <v>3.852215999999999</v>
+        <v>3.8329065</v>
       </c>
       <c r="O74">
-        <v>0.65487672</v>
+        <v>0.6515941049999999</v>
       </c>
       <c r="P74">
-        <v>3.19733928</v>
+        <v>3.181312395</v>
       </c>
       <c r="Q74">
-        <v>5.26733928</v>
+        <v>5.251312394999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1790140047071357</v>
+        <v>0.1836802503563356</v>
       </c>
       <c r="T74">
-        <v>3.076535905476574</v>
+        <v>3.184301393910753</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.770812294466454</v>
+        <v>3.719157331528557</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0867353375962106</v>
+        <v>0.08671387387442324</v>
       </c>
       <c r="C75">
-        <v>8.049498871586596</v>
+        <v>7.740529350403961</v>
       </c>
       <c r="D75">
-        <v>24.7044988715866</v>
+        <v>24.71052935040396</v>
       </c>
       <c r="E75">
-        <v>3.295000000000002</v>
+        <v>3.609999999999999</v>
       </c>
       <c r="F75">
-        <v>22.995</v>
+        <v>23.31</v>
       </c>
       <c r="G75">
         <v>6.34</v>
@@ -7431,28 +7431,28 @@
         <v>5.2425</v>
       </c>
       <c r="M75">
-        <v>1.4095935</v>
+        <v>1.428903</v>
       </c>
       <c r="N75">
-        <v>3.8329065</v>
+        <v>3.813597</v>
       </c>
       <c r="O75">
-        <v>0.6515941049999999</v>
+        <v>0.64831149</v>
       </c>
       <c r="P75">
-        <v>3.181312395</v>
+        <v>3.165285509999999</v>
       </c>
       <c r="Q75">
-        <v>5.251312394999999</v>
+        <v>5.235285509999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1836802503563356</v>
+        <v>0.1887054379785509</v>
       </c>
       <c r="T75">
-        <v>3.184301393910753</v>
+        <v>3.300356535301407</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.719157331528557</v>
+        <v>3.668898448670063</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08671387387442324</v>
+        <v>0.08669241015263587</v>
       </c>
       <c r="C76">
-        <v>7.740529350403961</v>
+        <v>7.431562774073949</v>
       </c>
       <c r="D76">
-        <v>24.71052935040396</v>
+        <v>24.71656277407395</v>
       </c>
       <c r="E76">
-        <v>3.609999999999999</v>
+        <v>3.925000000000001</v>
       </c>
       <c r="F76">
-        <v>23.31</v>
+        <v>23.625</v>
       </c>
       <c r="G76">
         <v>6.34</v>
@@ -7513,28 +7513,28 @@
         <v>5.2425</v>
       </c>
       <c r="M76">
-        <v>1.428903</v>
+        <v>1.4482125</v>
       </c>
       <c r="N76">
-        <v>3.813597</v>
+        <v>3.7942875</v>
       </c>
       <c r="O76">
-        <v>0.64831149</v>
+        <v>0.6450288750000001</v>
       </c>
       <c r="P76">
-        <v>3.165285509999999</v>
+        <v>3.149258625</v>
       </c>
       <c r="Q76">
-        <v>5.235285509999999</v>
+        <v>5.219258625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1887054379785509</v>
+        <v>0.1941326406105435</v>
       </c>
       <c r="T76">
-        <v>3.300356535301407</v>
+        <v>3.425696088003314</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.668898448670063</v>
+        <v>3.619979802687796</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08669241015263587</v>
+        <v>0.08667094643084849</v>
       </c>
       <c r="C77">
-        <v>7.431562774073949</v>
+        <v>7.122599144754179</v>
       </c>
       <c r="D77">
-        <v>24.71656277407395</v>
+        <v>24.72259914475418</v>
       </c>
       <c r="E77">
-        <v>3.925000000000001</v>
+        <v>4.240000000000002</v>
       </c>
       <c r="F77">
-        <v>23.625</v>
+        <v>23.94</v>
       </c>
       <c r="G77">
         <v>6.34</v>
@@ -7595,28 +7595,28 @@
         <v>5.2425</v>
       </c>
       <c r="M77">
-        <v>1.4482125</v>
+        <v>1.467522</v>
       </c>
       <c r="N77">
-        <v>3.7942875</v>
+        <v>3.774978</v>
       </c>
       <c r="O77">
-        <v>0.6450288750000001</v>
+        <v>0.64174626</v>
       </c>
       <c r="P77">
-        <v>3.149258625</v>
+        <v>3.13323174</v>
       </c>
       <c r="Q77">
-        <v>5.219258625</v>
+        <v>5.20323174</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1941326406105435</v>
+        <v>0.2000121101285354</v>
       </c>
       <c r="T77">
-        <v>3.425696088003314</v>
+        <v>3.561480603430379</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.619979802687796</v>
+        <v>3.572348489494536</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08667094643084849</v>
+        <v>0.08664948270906113</v>
       </c>
       <c r="C78">
-        <v>7.122599144754179</v>
+        <v>6.81363846460436</v>
       </c>
       <c r="D78">
-        <v>24.72259914475418</v>
+        <v>24.72863846460436</v>
       </c>
       <c r="E78">
-        <v>4.240000000000002</v>
+        <v>4.555</v>
       </c>
       <c r="F78">
-        <v>23.94</v>
+        <v>24.255</v>
       </c>
       <c r="G78">
         <v>6.34</v>
@@ -7677,28 +7677,28 @@
         <v>5.2425</v>
       </c>
       <c r="M78">
-        <v>1.467522</v>
+        <v>1.4868315</v>
       </c>
       <c r="N78">
-        <v>3.774978</v>
+        <v>3.7556685</v>
       </c>
       <c r="O78">
-        <v>0.64174626</v>
+        <v>0.638463645</v>
       </c>
       <c r="P78">
-        <v>3.13323174</v>
+        <v>3.117204855</v>
       </c>
       <c r="Q78">
-        <v>5.20323174</v>
+        <v>5.187204854999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2000121101285354</v>
+        <v>0.2064028378654832</v>
       </c>
       <c r="T78">
-        <v>3.561480603430379</v>
+        <v>3.709072468025016</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.572348489494536</v>
+        <v>3.525954353267334</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08664948270906113</v>
+        <v>0.08844073898727375</v>
       </c>
       <c r="C79">
-        <v>6.81363846460436</v>
+        <v>6.004575816761317</v>
       </c>
       <c r="D79">
-        <v>24.72863846460436</v>
+        <v>24.23457581676132</v>
       </c>
       <c r="E79">
-        <v>4.555</v>
+        <v>4.870000000000001</v>
       </c>
       <c r="F79">
-        <v>24.255</v>
+        <v>24.57</v>
       </c>
       <c r="G79">
         <v>6.34</v>
@@ -7759,45 +7759,45 @@
         <v>5.2425</v>
       </c>
       <c r="M79">
-        <v>1.4868315</v>
+        <v>1.574937</v>
       </c>
       <c r="N79">
-        <v>3.7556685</v>
+        <v>3.667562999999999</v>
       </c>
       <c r="O79">
-        <v>0.638463645</v>
+        <v>0.62348571</v>
       </c>
       <c r="P79">
-        <v>3.117204855</v>
+        <v>3.04407729</v>
       </c>
       <c r="Q79">
-        <v>5.187204854999999</v>
+        <v>5.114077289999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2064028378654832</v>
+        <v>0.2133745408512444</v>
       </c>
       <c r="T79">
-        <v>3.709072468025016</v>
+        <v>3.870081774855529</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.17</v>
       </c>
       <c r="W79">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.525954353267334</v>
+        <v>3.328704576754498</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08844073898727375</v>
+        <v>0.08844251526548638</v>
       </c>
       <c r="C80">
-        <v>6.004575816761317</v>
+        <v>5.689095683383751</v>
       </c>
       <c r="D80">
-        <v>24.23457581676132</v>
+        <v>24.23409568338375</v>
       </c>
       <c r="E80">
-        <v>4.870000000000001</v>
+        <v>5.185000000000002</v>
       </c>
       <c r="F80">
-        <v>24.57</v>
+        <v>24.885</v>
       </c>
       <c r="G80">
         <v>6.34</v>
@@ -7841,28 +7841,28 @@
         <v>5.2425</v>
       </c>
       <c r="M80">
-        <v>1.574937</v>
+        <v>1.5951285</v>
       </c>
       <c r="N80">
-        <v>3.667562999999999</v>
+        <v>3.647371499999999</v>
       </c>
       <c r="O80">
-        <v>0.62348571</v>
+        <v>0.6200531549999999</v>
       </c>
       <c r="P80">
-        <v>3.04407729</v>
+        <v>3.027318344999999</v>
       </c>
       <c r="Q80">
-        <v>5.114077289999999</v>
+        <v>5.097318345</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2133745408512444</v>
+        <v>0.2210102155499352</v>
       </c>
       <c r="T80">
-        <v>3.870081774855529</v>
+        <v>4.046425301384184</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.328704576754498</v>
+        <v>3.286569075782922</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08844251526548638</v>
+        <v>0.08844429154369901</v>
       </c>
       <c r="C81">
-        <v>5.689095683383751</v>
+        <v>5.373615569030534</v>
       </c>
       <c r="D81">
-        <v>24.23409568338375</v>
+        <v>24.23361556903054</v>
       </c>
       <c r="E81">
-        <v>5.185000000000002</v>
+        <v>5.500000000000004</v>
       </c>
       <c r="F81">
-        <v>24.885</v>
+        <v>25.2</v>
       </c>
       <c r="G81">
         <v>6.34</v>
@@ -7923,28 +7923,28 @@
         <v>5.2425</v>
       </c>
       <c r="M81">
-        <v>1.5951285</v>
+        <v>1.61532</v>
       </c>
       <c r="N81">
-        <v>3.647371499999999</v>
+        <v>3.627179999999999</v>
       </c>
       <c r="O81">
-        <v>0.6200531549999999</v>
+        <v>0.6166205999999999</v>
       </c>
       <c r="P81">
-        <v>3.027318344999999</v>
+        <v>3.010559399999999</v>
       </c>
       <c r="Q81">
-        <v>5.097318345</v>
+        <v>5.080559399999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2210102155499352</v>
+        <v>0.2294094577184951</v>
       </c>
       <c r="T81">
-        <v>4.046425301384184</v>
+        <v>4.240403180565707</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.286569075782922</v>
+        <v>3.245486962335635</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08844429154369901</v>
+        <v>0.08844606782191165</v>
       </c>
       <c r="C82">
-        <v>5.373615569030534</v>
+        <v>5.058135473700531</v>
       </c>
       <c r="D82">
-        <v>24.23361556903054</v>
+        <v>24.23313547370053</v>
       </c>
       <c r="E82">
-        <v>5.500000000000004</v>
+        <v>5.815000000000001</v>
       </c>
       <c r="F82">
-        <v>25.2</v>
+        <v>25.515</v>
       </c>
       <c r="G82">
         <v>6.34</v>
@@ -8005,28 +8005,28 @@
         <v>5.2425</v>
       </c>
       <c r="M82">
-        <v>1.61532</v>
+        <v>1.6355115</v>
       </c>
       <c r="N82">
-        <v>3.627179999999999</v>
+        <v>3.606988499999999</v>
       </c>
       <c r="O82">
-        <v>0.6166205999999999</v>
+        <v>0.6131880449999999</v>
       </c>
       <c r="P82">
-        <v>3.010559399999999</v>
+        <v>2.993800455</v>
       </c>
       <c r="Q82">
-        <v>5.080559399999999</v>
+        <v>5.063800454999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2294094577184951</v>
+        <v>0.2386928306416403</v>
       </c>
       <c r="T82">
-        <v>4.240403180565707</v>
+        <v>4.454799783871601</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.245486962335635</v>
+        <v>3.205419222059887</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08844606782191165</v>
+        <v>0.08844784410012428</v>
       </c>
       <c r="C83">
-        <v>5.058135473700531</v>
+        <v>4.742655397392614</v>
       </c>
       <c r="D83">
-        <v>24.23313547370053</v>
+        <v>24.23265539739262</v>
       </c>
       <c r="E83">
-        <v>5.815000000000001</v>
+        <v>6.130000000000003</v>
       </c>
       <c r="F83">
-        <v>25.515</v>
+        <v>25.83</v>
       </c>
       <c r="G83">
         <v>6.34</v>
@@ -8087,28 +8087,28 @@
         <v>5.2425</v>
       </c>
       <c r="M83">
-        <v>1.6355115</v>
+        <v>1.655703</v>
       </c>
       <c r="N83">
-        <v>3.606988499999999</v>
+        <v>3.586797</v>
       </c>
       <c r="O83">
-        <v>0.6131880449999999</v>
+        <v>0.60975549</v>
       </c>
       <c r="P83">
-        <v>2.993800455</v>
+        <v>2.97704151</v>
       </c>
       <c r="Q83">
-        <v>5.063800454999999</v>
+        <v>5.04704151</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2386928306416403</v>
+        <v>0.2490076894451349</v>
       </c>
       <c r="T83">
-        <v>4.454799783871601</v>
+        <v>4.693018231989259</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.205419222059887</v>
+        <v>3.166328743742084</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08844784410012428</v>
+        <v>0.0884496203783369</v>
       </c>
       <c r="C84">
-        <v>4.742655397392614</v>
+        <v>4.427175340105659</v>
       </c>
       <c r="D84">
-        <v>24.23265539739262</v>
+        <v>24.23217534010566</v>
       </c>
       <c r="E84">
-        <v>6.130000000000003</v>
+        <v>6.445000000000004</v>
       </c>
       <c r="F84">
-        <v>25.83</v>
+        <v>26.145</v>
       </c>
       <c r="G84">
         <v>6.34</v>
@@ -8169,28 +8169,28 @@
         <v>5.2425</v>
       </c>
       <c r="M84">
-        <v>1.655703</v>
+        <v>1.6758945</v>
       </c>
       <c r="N84">
-        <v>3.586797</v>
+        <v>3.5666055</v>
       </c>
       <c r="O84">
-        <v>0.60975549</v>
+        <v>0.606322935</v>
       </c>
       <c r="P84">
-        <v>2.97704151</v>
+        <v>2.960282565</v>
       </c>
       <c r="Q84">
-        <v>5.04704151</v>
+        <v>5.030282564999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2490076894451349</v>
+        <v>0.2605360610490406</v>
       </c>
       <c r="T84">
-        <v>4.693018231989259</v>
+        <v>4.959262379885466</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.166328743742084</v>
+        <v>3.128180204660854</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0884496203783369</v>
+        <v>0.08845139665654952</v>
       </c>
       <c r="C85">
-        <v>4.427175340105659</v>
+        <v>4.111695301838527</v>
       </c>
       <c r="D85">
-        <v>24.23217534010566</v>
+        <v>24.23169530183853</v>
       </c>
       <c r="E85">
-        <v>6.445000000000004</v>
+        <v>6.760000000000002</v>
       </c>
       <c r="F85">
-        <v>26.145</v>
+        <v>26.46</v>
       </c>
       <c r="G85">
         <v>6.34</v>
@@ -8251,28 +8251,28 @@
         <v>5.2425</v>
       </c>
       <c r="M85">
-        <v>1.6758945</v>
+        <v>1.696086</v>
       </c>
       <c r="N85">
-        <v>3.5666055</v>
+        <v>3.546414</v>
       </c>
       <c r="O85">
-        <v>0.606322935</v>
+        <v>0.6028903799999999</v>
       </c>
       <c r="P85">
-        <v>2.960282565</v>
+        <v>2.94352362</v>
       </c>
       <c r="Q85">
-        <v>5.030282564999999</v>
+        <v>5.013523619999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2605360610490406</v>
+        <v>0.2735054791034347</v>
       </c>
       <c r="T85">
-        <v>4.959262379885466</v>
+        <v>5.2587870462687</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.128180204660854</v>
+        <v>3.090939964129177</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08845139665654952</v>
+        <v>0.08845317293476217</v>
       </c>
       <c r="C86">
-        <v>4.11169530183853</v>
+        <v>3.79621528259009</v>
       </c>
       <c r="D86">
-        <v>24.23169530183853</v>
+        <v>24.23121528259009</v>
       </c>
       <c r="E86">
-        <v>6.759999999999998</v>
+        <v>7.074999999999999</v>
       </c>
       <c r="F86">
-        <v>26.46</v>
+        <v>26.775</v>
       </c>
       <c r="G86">
         <v>6.34</v>
@@ -8333,28 +8333,28 @@
         <v>5.2425</v>
       </c>
       <c r="M86">
-        <v>1.696086</v>
+        <v>1.7162775</v>
       </c>
       <c r="N86">
-        <v>3.546414</v>
+        <v>3.526222499999999</v>
       </c>
       <c r="O86">
-        <v>0.6028903799999999</v>
+        <v>0.5994578249999999</v>
       </c>
       <c r="P86">
-        <v>2.94352362</v>
+        <v>2.926764674999999</v>
       </c>
       <c r="Q86">
-        <v>5.013523619999999</v>
+        <v>4.996764675</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2735054791034345</v>
+        <v>0.2882041528984144</v>
       </c>
       <c r="T86">
-        <v>5.258787046268696</v>
+        <v>5.59824833483636</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.090939964129177</v>
+        <v>3.054575964551187</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08845317293476217</v>
+        <v>0.08845494921297478</v>
       </c>
       <c r="C87">
-        <v>3.79621528259009</v>
+        <v>3.480735282359216</v>
       </c>
       <c r="D87">
-        <v>24.23121528259009</v>
+        <v>24.23073528235922</v>
       </c>
       <c r="E87">
-        <v>7.074999999999999</v>
+        <v>7.390000000000001</v>
       </c>
       <c r="F87">
-        <v>26.775</v>
+        <v>27.09</v>
       </c>
       <c r="G87">
         <v>6.34</v>
@@ -8415,28 +8415,28 @@
         <v>5.2425</v>
       </c>
       <c r="M87">
-        <v>1.7162775</v>
+        <v>1.736469</v>
       </c>
       <c r="N87">
-        <v>3.526222499999999</v>
+        <v>3.506031</v>
       </c>
       <c r="O87">
-        <v>0.5994578249999999</v>
+        <v>0.5960252699999999</v>
       </c>
       <c r="P87">
-        <v>2.926764674999999</v>
+        <v>2.91000573</v>
       </c>
       <c r="Q87">
-        <v>4.996764675</v>
+        <v>4.98000573</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2882041528984144</v>
+        <v>0.3050026372355342</v>
       </c>
       <c r="T87">
-        <v>5.59824833483636</v>
+        <v>5.986204093199404</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.054575964551187</v>
+        <v>3.019057639381987</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08845494921297478</v>
+        <v>0.09408910549118743</v>
       </c>
       <c r="C88">
-        <v>3.480735282359216</v>
+        <v>1.73326398561408</v>
       </c>
       <c r="D88">
-        <v>24.23073528235922</v>
+        <v>22.79826398561408</v>
       </c>
       <c r="E88">
-        <v>7.390000000000001</v>
+        <v>7.705000000000002</v>
       </c>
       <c r="F88">
-        <v>27.09</v>
+        <v>27.405</v>
       </c>
       <c r="G88">
         <v>6.34</v>
@@ -8497,45 +8497,45 @@
         <v>5.2425</v>
       </c>
       <c r="M88">
-        <v>1.736469</v>
+        <v>1.9704195</v>
       </c>
       <c r="N88">
-        <v>3.506031</v>
+        <v>3.2720805</v>
       </c>
       <c r="O88">
-        <v>0.5960252699999999</v>
+        <v>0.5562536849999999</v>
       </c>
       <c r="P88">
-        <v>2.91000573</v>
+        <v>2.715826815</v>
       </c>
       <c r="Q88">
-        <v>4.98000573</v>
+        <v>4.785826815</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3050026372355342</v>
+        <v>0.3243855037783648</v>
       </c>
       <c r="T88">
-        <v>5.986204093199404</v>
+        <v>6.433845352849072</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.17</v>
       </c>
       <c r="W88">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.019057639381987</v>
+        <v>2.660600953248788</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09408910549118743</v>
+        <v>0.09415562176940007</v>
       </c>
       <c r="C89">
-        <v>1.73326398561408</v>
+        <v>1.40236325208069</v>
       </c>
       <c r="D89">
-        <v>22.79826398561408</v>
+        <v>22.78236325208069</v>
       </c>
       <c r="E89">
-        <v>7.705000000000002</v>
+        <v>8.02</v>
       </c>
       <c r="F89">
-        <v>27.405</v>
+        <v>27.72</v>
       </c>
       <c r="G89">
         <v>6.34</v>
@@ -8579,28 +8579,28 @@
         <v>5.2425</v>
       </c>
       <c r="M89">
-        <v>1.9704195</v>
+        <v>1.993068</v>
       </c>
       <c r="N89">
-        <v>3.2720805</v>
+        <v>3.249432</v>
       </c>
       <c r="O89">
-        <v>0.5562536849999999</v>
+        <v>0.55240344</v>
       </c>
       <c r="P89">
-        <v>2.715826815</v>
+        <v>2.69702856</v>
       </c>
       <c r="Q89">
-        <v>4.785826815</v>
+        <v>4.76702856</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3243855037783648</v>
+        <v>0.3469988480783338</v>
       </c>
       <c r="T89">
-        <v>6.433845352849072</v>
+        <v>6.956093489107016</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.660600953248788</v>
+        <v>2.630366851507324</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09415562176940007</v>
+        <v>0.09422213804761267</v>
       </c>
       <c r="C90">
-        <v>1.40236325208069</v>
+        <v>1.071484683139353</v>
       </c>
       <c r="D90">
-        <v>22.78236325208069</v>
+        <v>22.76648468313935</v>
       </c>
       <c r="E90">
-        <v>8.02</v>
+        <v>8.335000000000001</v>
       </c>
       <c r="F90">
-        <v>27.72</v>
+        <v>28.035</v>
       </c>
       <c r="G90">
         <v>6.34</v>
@@ -8661,28 +8661,28 @@
         <v>5.2425</v>
       </c>
       <c r="M90">
-        <v>1.993068</v>
+        <v>2.0157165</v>
       </c>
       <c r="N90">
-        <v>3.249432</v>
+        <v>3.226783499999999</v>
       </c>
       <c r="O90">
-        <v>0.55240344</v>
+        <v>0.5485531949999999</v>
       </c>
       <c r="P90">
-        <v>2.69702856</v>
+        <v>2.678230305</v>
       </c>
       <c r="Q90">
-        <v>4.76702856</v>
+        <v>4.748230305</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3469988480783338</v>
+        <v>0.3737237095237517</v>
       </c>
       <c r="T90">
-        <v>6.956093489107016</v>
+        <v>7.573295831957314</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.630366851507324</v>
+        <v>2.600812167782522</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09422213804761267</v>
+        <v>0.09428865432582531</v>
       </c>
       <c r="C91">
-        <v>1.071484683139353</v>
+        <v>0.7406282324783184</v>
       </c>
       <c r="D91">
-        <v>22.76648468313935</v>
+        <v>22.75062823247832</v>
       </c>
       <c r="E91">
-        <v>8.335000000000001</v>
+        <v>8.650000000000002</v>
       </c>
       <c r="F91">
-        <v>28.035</v>
+        <v>28.35</v>
       </c>
       <c r="G91">
         <v>6.34</v>
@@ -8743,28 +8743,28 @@
         <v>5.2425</v>
       </c>
       <c r="M91">
-        <v>2.0157165</v>
+        <v>2.038365</v>
       </c>
       <c r="N91">
-        <v>3.226783499999999</v>
+        <v>3.204135</v>
       </c>
       <c r="O91">
-        <v>0.5485531949999999</v>
+        <v>0.5447029499999999</v>
       </c>
       <c r="P91">
-        <v>2.678230305</v>
+        <v>2.659432049999999</v>
       </c>
       <c r="Q91">
-        <v>4.748230305</v>
+        <v>4.72943205</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3737237095237517</v>
+        <v>0.4057935432582532</v>
       </c>
       <c r="T91">
-        <v>7.573295831957314</v>
+        <v>8.313938643377673</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.600812167782522</v>
+        <v>2.571914254807161</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09428865432582531</v>
+        <v>0.09435517060403795</v>
       </c>
       <c r="C92">
-        <v>0.7406282324783184</v>
+        <v>0.4097938539148025</v>
       </c>
       <c r="D92">
-        <v>22.75062823247832</v>
+        <v>22.73479385391481</v>
       </c>
       <c r="E92">
-        <v>8.650000000000002</v>
+        <v>8.965000000000003</v>
       </c>
       <c r="F92">
-        <v>28.35</v>
+        <v>28.665</v>
       </c>
       <c r="G92">
         <v>6.34</v>
@@ -8825,28 +8825,28 @@
         <v>5.2425</v>
       </c>
       <c r="M92">
-        <v>2.038365</v>
+        <v>2.0610135</v>
       </c>
       <c r="N92">
-        <v>3.204135</v>
+        <v>3.181486499999999</v>
       </c>
       <c r="O92">
-        <v>0.5447029499999999</v>
+        <v>0.5408527049999999</v>
       </c>
       <c r="P92">
-        <v>2.659432049999999</v>
+        <v>2.640633794999999</v>
       </c>
       <c r="Q92">
-        <v>4.72943205</v>
+        <v>4.710633795</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4057935432582532</v>
+        <v>0.4449900067115328</v>
       </c>
       <c r="T92">
-        <v>8.313938643377673</v>
+        <v>9.219168746224776</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.571914254807161</v>
+        <v>2.543651460798291</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09435517060403795</v>
+        <v>0.09442168688225057</v>
       </c>
       <c r="C93">
-        <v>0.4097938539148025</v>
+        <v>0.07898150139448745</v>
       </c>
       <c r="D93">
-        <v>22.73479385391481</v>
+        <v>22.71898150139449</v>
       </c>
       <c r="E93">
-        <v>8.965000000000003</v>
+        <v>9.280000000000001</v>
       </c>
       <c r="F93">
-        <v>28.665</v>
+        <v>28.98</v>
       </c>
       <c r="G93">
         <v>6.34</v>
@@ -8907,28 +8907,28 @@
         <v>5.2425</v>
       </c>
       <c r="M93">
-        <v>2.0610135</v>
+        <v>2.083662</v>
       </c>
       <c r="N93">
-        <v>3.181486499999999</v>
+        <v>3.158837999999999</v>
       </c>
       <c r="O93">
-        <v>0.5408527049999999</v>
+        <v>0.53700246</v>
       </c>
       <c r="P93">
-        <v>2.640633794999999</v>
+        <v>2.621835539999999</v>
       </c>
       <c r="Q93">
-        <v>4.710633795</v>
+        <v>4.69183554</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4449900067115328</v>
+        <v>0.4939855860281324</v>
       </c>
       <c r="T93">
-        <v>9.219168746224776</v>
+        <v>10.35070637478366</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.543651460798291</v>
+        <v>2.516003075354831</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09442168688225057</v>
+        <v>0.0974986131604632</v>
       </c>
       <c r="C94">
-        <v>0.07898150139448745</v>
+        <v>-0.9441776718409542</v>
       </c>
       <c r="D94">
-        <v>22.71898150139449</v>
+        <v>22.01082232815905</v>
       </c>
       <c r="E94">
-        <v>9.280000000000001</v>
+        <v>9.595000000000002</v>
       </c>
       <c r="F94">
-        <v>28.98</v>
+        <v>29.295</v>
       </c>
       <c r="G94">
         <v>6.34</v>
@@ -8989,45 +8989,45 @@
         <v>5.2425</v>
       </c>
       <c r="M94">
-        <v>2.083662</v>
+        <v>2.220561</v>
       </c>
       <c r="N94">
-        <v>3.158837999999999</v>
+        <v>3.021938999999999</v>
       </c>
       <c r="O94">
-        <v>0.53700246</v>
+        <v>0.5137296299999999</v>
       </c>
       <c r="P94">
-        <v>2.621835539999999</v>
+        <v>2.508209369999999</v>
       </c>
       <c r="Q94">
-        <v>4.69183554</v>
+        <v>4.57820937</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4939855860281324</v>
+        <v>0.5569799022923317</v>
       </c>
       <c r="T94">
-        <v>10.35070637478366</v>
+        <v>11.80554046864508</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.17</v>
       </c>
       <c r="W94">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.516003075354831</v>
+        <v>2.360889883232209</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0974986131604632</v>
+        <v>0.09759749943867582</v>
       </c>
       <c r="C95">
-        <v>-0.9441776718409542</v>
+        <v>-1.28120502921443</v>
       </c>
       <c r="D95">
-        <v>22.01082232815905</v>
+        <v>21.98879497078557</v>
       </c>
       <c r="E95">
-        <v>9.595000000000002</v>
+        <v>9.910000000000004</v>
       </c>
       <c r="F95">
-        <v>29.295</v>
+        <v>29.61</v>
       </c>
       <c r="G95">
         <v>6.34</v>
@@ -9071,28 +9071,28 @@
         <v>5.2425</v>
       </c>
       <c r="M95">
-        <v>2.220561</v>
+        <v>2.244438000000001</v>
       </c>
       <c r="N95">
-        <v>3.021938999999999</v>
+        <v>2.998061999999999</v>
       </c>
       <c r="O95">
-        <v>0.5137296299999999</v>
+        <v>0.5096705399999999</v>
       </c>
       <c r="P95">
-        <v>2.508209369999999</v>
+        <v>2.488391459999999</v>
       </c>
       <c r="Q95">
-        <v>4.57820937</v>
+        <v>4.558391459999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5569799022923317</v>
+        <v>0.6409723239779309</v>
       </c>
       <c r="T95">
-        <v>11.80554046864508</v>
+        <v>13.7453192604603</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.360889883232209</v>
+        <v>2.335774033410591</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09759749943867582</v>
+        <v>0.09769638571688846</v>
       </c>
       <c r="C96">
-        <v>-1.28120502921443</v>
+        <v>-1.618188342855042</v>
       </c>
       <c r="D96">
-        <v>21.98879497078557</v>
+        <v>21.96681165714496</v>
       </c>
       <c r="E96">
-        <v>9.910000000000004</v>
+        <v>10.225</v>
       </c>
       <c r="F96">
-        <v>29.61</v>
+        <v>29.925</v>
       </c>
       <c r="G96">
         <v>6.34</v>
@@ -9153,28 +9153,28 @@
         <v>5.2425</v>
       </c>
       <c r="M96">
-        <v>2.244438000000001</v>
+        <v>2.268315</v>
       </c>
       <c r="N96">
-        <v>2.998061999999999</v>
+        <v>2.974184999999999</v>
       </c>
       <c r="O96">
-        <v>0.5096705399999999</v>
+        <v>0.50561145</v>
       </c>
       <c r="P96">
-        <v>2.488391459999999</v>
+        <v>2.468573549999999</v>
       </c>
       <c r="Q96">
-        <v>4.558391459999999</v>
+        <v>4.538573549999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6409723239779309</v>
+        <v>0.7585617143377701</v>
       </c>
       <c r="T96">
-        <v>13.7453192604603</v>
+        <v>16.46100956900162</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.335774033410591</v>
+        <v>2.311186938322058</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09769638571688846</v>
+        <v>0.09779527199510107</v>
       </c>
       <c r="C97">
-        <v>-1.618188342855042</v>
+        <v>-1.955127744729118</v>
       </c>
       <c r="D97">
-        <v>21.96681165714496</v>
+        <v>21.94487225527088</v>
       </c>
       <c r="E97">
-        <v>10.225</v>
+        <v>10.54</v>
       </c>
       <c r="F97">
-        <v>29.925</v>
+        <v>30.24</v>
       </c>
       <c r="G97">
         <v>6.34</v>
@@ -9235,28 +9235,28 @@
         <v>5.2425</v>
       </c>
       <c r="M97">
-        <v>2.268315</v>
+        <v>2.292192</v>
       </c>
       <c r="N97">
-        <v>2.974184999999999</v>
+        <v>2.950307999999999</v>
       </c>
       <c r="O97">
-        <v>0.50561145</v>
+        <v>0.5015523599999999</v>
       </c>
       <c r="P97">
-        <v>2.468573549999999</v>
+        <v>2.448755639999999</v>
       </c>
       <c r="Q97">
-        <v>4.538573549999999</v>
+        <v>4.518755639999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7585617143377701</v>
+        <v>0.9349457998775287</v>
       </c>
       <c r="T97">
-        <v>16.46100956900162</v>
+        <v>20.5345450318136</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.311186938322058</v>
+        <v>2.287112074381203</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09779527199510107</v>
+        <v>0.09789415827331371</v>
       </c>
       <c r="C98">
-        <v>-1.955127744729115</v>
+        <v>-2.292023366276315</v>
       </c>
       <c r="D98">
-        <v>21.94487225527088</v>
+        <v>21.92297663372369</v>
       </c>
       <c r="E98">
-        <v>10.54</v>
+        <v>10.855</v>
       </c>
       <c r="F98">
-        <v>30.24</v>
+        <v>30.555</v>
       </c>
       <c r="G98">
         <v>6.34</v>
@@ -9317,28 +9317,28 @@
         <v>5.2425</v>
       </c>
       <c r="M98">
-        <v>2.292192</v>
+        <v>2.316069</v>
       </c>
       <c r="N98">
-        <v>2.950308</v>
+        <v>2.926431</v>
       </c>
       <c r="O98">
-        <v>0.50155236</v>
+        <v>0.49749327</v>
       </c>
       <c r="P98">
-        <v>2.44875564</v>
+        <v>2.428937729999999</v>
       </c>
       <c r="Q98">
-        <v>4.51875564</v>
+        <v>4.49893773</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9349457998775264</v>
+        <v>1.228919275777123</v>
       </c>
       <c r="T98">
-        <v>20.53454503181354</v>
+        <v>27.32377080316681</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.287112074381203</v>
+        <v>2.263533599387583</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09789415827331371</v>
+        <v>0.09799304455152635</v>
       </c>
       <c r="C99">
-        <v>-2.292023366276315</v>
+        <v>-2.628875338412218</v>
       </c>
       <c r="D99">
-        <v>21.92297663372369</v>
+        <v>21.90112466158778</v>
       </c>
       <c r="E99">
-        <v>10.855</v>
+        <v>11.17</v>
       </c>
       <c r="F99">
-        <v>30.555</v>
+        <v>30.87</v>
       </c>
       <c r="G99">
         <v>6.34</v>
@@ -9399,28 +9399,28 @@
         <v>5.2425</v>
       </c>
       <c r="M99">
-        <v>2.316069</v>
+        <v>2.339946</v>
       </c>
       <c r="N99">
-        <v>2.926431</v>
+        <v>2.902553999999999</v>
       </c>
       <c r="O99">
-        <v>0.49749327</v>
+        <v>0.4934341799999999</v>
       </c>
       <c r="P99">
-        <v>2.428937729999999</v>
+        <v>2.409119819999999</v>
       </c>
       <c r="Q99">
-        <v>4.49893773</v>
+        <v>4.479119819999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.228919275777123</v>
+        <v>1.816866227576316</v>
       </c>
       <c r="T99">
-        <v>27.32377080316681</v>
+        <v>40.90222234587335</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.263533599387583</v>
+        <v>2.240436317761179</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09799304455152635</v>
+        <v>0.09809193082973897</v>
       </c>
       <c r="C100">
-        <v>-2.628875338412218</v>
+        <v>-2.965683791530957</v>
       </c>
       <c r="D100">
-        <v>21.90112466158778</v>
+        <v>21.87931620846904</v>
       </c>
       <c r="E100">
-        <v>11.17</v>
+        <v>11.485</v>
       </c>
       <c r="F100">
-        <v>30.87</v>
+        <v>31.185</v>
       </c>
       <c r="G100">
         <v>6.34</v>
@@ -9481,28 +9481,28 @@
         <v>5.2425</v>
       </c>
       <c r="M100">
-        <v>2.339946</v>
+        <v>2.363823</v>
       </c>
       <c r="N100">
-        <v>2.902553999999999</v>
+        <v>2.878677</v>
       </c>
       <c r="O100">
-        <v>0.4934341799999999</v>
+        <v>0.48937509</v>
       </c>
       <c r="P100">
-        <v>2.409119819999999</v>
+        <v>2.389301909999999</v>
       </c>
       <c r="Q100">
-        <v>4.479119819999999</v>
+        <v>4.459301909999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.816866227576316</v>
+        <v>3.580707082973894</v>
       </c>
       <c r="T100">
-        <v>40.90222234587335</v>
+        <v>81.63757697399295</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.240436317761179</v>
+        <v>2.217805647884803</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09809193082973897</v>
-      </c>
-      <c r="C101">
-        <v>-2.965683791530957</v>
-      </c>
-      <c r="D101">
-        <v>21.87931620846904</v>
-      </c>
-      <c r="E101">
-        <v>11.485</v>
-      </c>
-      <c r="F101">
-        <v>31.185</v>
-      </c>
-      <c r="G101">
-        <v>6.34</v>
-      </c>
-      <c r="H101">
-        <v>11.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.312499999999999</v>
-      </c>
-      <c r="K101">
-        <v>2.07</v>
-      </c>
-      <c r="L101">
-        <v>5.2425</v>
-      </c>
-      <c r="M101">
-        <v>2.363823</v>
-      </c>
-      <c r="N101">
-        <v>2.878677</v>
-      </c>
-      <c r="O101">
-        <v>0.48937509</v>
-      </c>
-      <c r="P101">
-        <v>2.389301909999999</v>
-      </c>
-      <c r="Q101">
-        <v>4.459301909999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.580707082973894</v>
-      </c>
-      <c r="T101">
-        <v>81.63757697399295</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.17</v>
-      </c>
-      <c r="W101">
-        <v>0.062914</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.217805647884803</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
